--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ankurdixit/Downloads/ankur_academic_site_percentage_layout 20/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ankurdixit/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D39BBB9-32AA-7B46-95E5-735EC71B7961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC494A1-1B9C-3943-86F8-2B1625CB4040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="20120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="175">
   <si>
     <t>Year</t>
   </si>
@@ -58,15 +58,9 @@
     <t>Cryospheric Processes Responsible for Lake Formation: A Review on Lake Types, Threats, Status, and Their Distribution within the Himalaya</t>
   </si>
   <si>
-    <t>Litan Kumar Mohanty, Parmanand Sharma, Rayees Ahmed, Ankur Dixit</t>
-  </si>
-  <si>
     <t>Climate Change, Water Resources, and Natural Hazards in the Himalayas</t>
   </si>
   <si>
-    <t>Springer chapter</t>
-  </si>
-  <si>
     <t>https://www.researchgate.net/publication/411981482_Cryospheric_Processes_Responsible_for_Lake_Formation_A_Review_on_Lake_Types_Threats_Status_and_Their_Distribution_within_the_Himalaya</t>
   </si>
   <si>
@@ -82,72 +76,33 @@
     <t>Sequence of events that led to the South Lhonak lake outburst flood in Sikkim, India</t>
   </si>
   <si>
-    <t>Litan Kumar Mohanty, Prateek Gantayat, Ankur Dixit, et al.</t>
-  </si>
-  <si>
     <t>Scientific Reports</t>
   </si>
   <si>
-    <t>Peer-reviewed article</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/403081019_Sequence_of_events_that_led_to_the_South_Lhonak_lake_outburst_flood_in_Sikkim_India</t>
-  </si>
-  <si>
     <t>High-resolution models better simulate historical snowpack declines in the Upper Colorado River Basin</t>
   </si>
   <si>
-    <t>Ankur Dixit, Stefan Rahimi, Lei Huang, Keith N. Musselman, Julie A. Vano, Nans Addor, Flavio Lehner</t>
-  </si>
-  <si>
     <t>Environmental Research Letters</t>
   </si>
   <si>
-    <t>21(5) · DOI: 10.1088/1748-9326/ae4113</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/400441424_High-resolution_models_better_simulate_historical_snowpack_declines_in_the_Upper_Colorado_River_Basin</t>
-  </si>
-  <si>
     <t>Revisiting the triggers of all GLOF events since 1950 in the Himalaya</t>
   </si>
   <si>
-    <t>Litan Kumar Mohanty, Anil Tiwari, Amit Kumar, et al., Ankur Dixit</t>
-  </si>
-  <si>
     <t>Natural Hazards</t>
   </si>
   <si>
-    <t>https://www.researchgate.net/publication/400684174_Revisiting_the_triggers_of_all_GLOF_events_since_1950_in_the_Himalaya</t>
-  </si>
-  <si>
     <t>Preprint</t>
   </si>
   <si>
     <t>Bias correction choices strongly shape California's projected megaflood risk</t>
   </si>
   <si>
-    <t>Stefan Rahimi, Lei Huang, Chad Thackeray, et al., Ankur Dixit</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/400333979_Bias_correction_choices_strongly_shape_California%27s_projected_megaflood_risk</t>
-  </si>
-  <si>
     <t>Optimizing WRF-Hydro Calibration in the Himalayan Basin: Precipitation Influence and Parameter Sensitivity Analysis</t>
   </si>
   <si>
-    <t>Ankur Dixit, Sandeep Sahany, Saroj Kanta Mishra, Flavio Lehner</t>
-  </si>
-  <si>
     <t>Journal of Hydrometeorology</t>
   </si>
   <si>
-    <t>26(3):345–363 · DOI: 10.1175/JHM-D-24-0096.1</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/388128130_Optimizing_WRF-Hydro_Calibration_in_the_Himalayan_Basin_Precipitation_Influence_and_Parameter_Sensitivity_Analysis</t>
-  </si>
-  <si>
     <t>Dataset / method</t>
   </si>
   <si>
@@ -166,24 +121,9 @@
     <t>Analyzing water level variability in Odisha: insights from multi-year data and spatial analysis</t>
   </si>
   <si>
-    <t>Litan Mohanty, Banajarani Panda, Sambit Samantaray, et al.</t>
-  </si>
-  <si>
     <t>Discover Applied Sciences</t>
   </si>
   <si>
-    <t>https://www.researchgate.net/publication/381921384_Analyzing_water_level_variability_in_Odisha_insights_from_multi-year_data_and_spatial_analysis</t>
-  </si>
-  <si>
-    <t>Ankur Dixit, Sandeep Sahany, Flavio Lehner, Saroj Kanta Mishra</t>
-  </si>
-  <si>
-    <t>Preprint version of 2025 Journal of Hydrometeorology article</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/379101652_Optimizing_WRF-Hydro_Calibration_in_the_Himalayan_Basin_Precipitation_Influence_and_Parameter_Sensitivity_Analysis</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -199,33 +139,15 @@
     <t>627, 130219</t>
   </si>
   <si>
-    <t>https://www.researchgate.net/publication/374304093_Modeling_the_Climate_Change_Impact_on_Hydroclimate_Fluxes_over_the_Beas_Basin_using_a_High-Resolution_Glacier-Atmosphere-Hydrology_Coupled_Setup</t>
-  </si>
-  <si>
     <t>Seasonal dependent suitability of physical parameterizations to simulate precipitation over the Himalayan headwater</t>
   </si>
   <si>
-    <t>Ankur Dixit, Sandeep Sahany, Saroj Kanta Mishra, Michel D. S. Mesquita</t>
-  </si>
-  <si>
-    <t>13, 4756 · DOI: 10.1038/s41598-023-31353-w</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/369478344_Seasonal_dependent_suitability_of_physical_parameterizations_to_simulate_precipitation_over_the_Himalayan_headwater</t>
-  </si>
-  <si>
     <t>Spatio-temporal assessment of regional scale evolution and distribution of glacial lakes in Himalaya</t>
   </si>
   <si>
-    <t>Litan Mohanty, Sabyasachi Maiti, Ankur Dixit</t>
-  </si>
-  <si>
     <t>Frontiers in Earth Science</t>
   </si>
   <si>
-    <t>https://www.researchgate.net/publication/367035010_Spatio-temporal_assessment_of_regional_scale_evolution_and_distribution_of_glacial_lakes_in_Himalaya</t>
-  </si>
-  <si>
     <t>Supplementary data</t>
   </si>
   <si>
@@ -244,24 +166,15 @@
     <t>Role of changing land use and land cover (LULC) on the 2018 megafloods over Kerala, India</t>
   </si>
   <si>
-    <t>Ankur Dixit, Sandeep Sahany, B. Rajagopalan, Sweta Choubey</t>
-  </si>
-  <si>
     <t>Climate Research</t>
   </si>
   <si>
-    <t>https://www.researchgate.net/publication/362126885_Role_of_changing_land_use_and_land_cover_LULC_on_the_2018_megafloods_over_Kerala_India</t>
-  </si>
-  <si>
     <t>Mapping Samudra Tapu glacier: A holistic approach utilizing radar and optical remote sensing data for glacier radar facies mapping and velocity estimation</t>
   </si>
   <si>
     <t>Advances in Space Research</t>
   </si>
   <si>
-    <t>https://www.researchgate.net/publication/364406815_Mapping_Samudra_Tapu_glacier_A_holistic_approach_utilizing_radar_and_optical_remote_sensing_data_for_glacier_radar_facies_mapping_and_velocity_estimation</t>
-  </si>
-  <si>
     <t>Poster</t>
   </si>
   <si>
@@ -283,18 +196,12 @@
     <t>Glacial changes over the Himalayan Beas basin under global warming</t>
   </si>
   <si>
-    <t>Ankur Dixit, Sandeep Sahany, A. V. Kulkarni</t>
-  </si>
-  <si>
     <t>Journal of Environmental Management</t>
   </si>
   <si>
     <t>295, 113101</t>
   </si>
   <si>
-    <t>https://www.researchgate.net/publication/352812925_Glacial_changes_over_the_Himalayan_Beas_basin_under_global_warming</t>
-  </si>
-  <si>
     <t>Non-linear Spectral Unmixing of Hyperspectral Data using Modified PPNMM</t>
   </si>
   <si>
@@ -304,45 +211,21 @@
     <t>Applied Computing and Geosciences</t>
   </si>
   <si>
-    <t>9, 100053 · DOI: 10.1016/j.acags.2021.100053</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/348480304_Non-linear_Spectral_Unmixing_of_Hyperspectral_Data_using_Modified_PPNMM</t>
-  </si>
-  <si>
     <t>Vertical stripe correction in Hyperion image using wavelet transformation and singular value decomposition (SVD)</t>
   </si>
   <si>
     <t>Geocarto International</t>
   </si>
   <si>
-    <t>https://www.researchgate.net/publication/346558575_Vertical_stripe_correction_in_Hyperion_image_using_wavelet_transformation_and_singular_value_decomposition_SVD</t>
-  </si>
-  <si>
-    <t>ROLE OF EARTH OBSERVATION DATA AND HYDROLOGICAL MODELING IN SUPPORTING UN SDGs IN NORTH WEST HIMALAYA</t>
-  </si>
-  <si>
-    <t>Shiv P. Aggarwal, Praveen K. Thakur, Bhaskar R. Nikam, Vaibhav Garg, et al., Ankur Dixit</t>
-  </si>
-  <si>
     <t>The International Archives of the Photogrammetry, Remote Sensing and Spatial Information Sciences</t>
   </si>
   <si>
-    <t>XLIII-B3-2020:853–860 · DOI: 10.5194/isprs-archives-XLIII-B3-2020-853-2020</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/343799399_ROLE_OF_EARTH_OBSERVATION_DATA_AND_HYDROLOGICAL_MODELING_IN_SUPPORTING_UN_SDGs_IN_NORTH_WEST_HIMALAYA</t>
-  </si>
-  <si>
     <t>Super-resolution mapping of hyperspectral data using Artificial Neural Network and wavelet</t>
   </si>
   <si>
     <t>Remote Sensing Applications: Society and Environment</t>
   </si>
   <si>
-    <t>https://www.researchgate.net/publication/343755543_Super-resolution_mapping_of_hyperspectral_data_using_Artificial_Neural_Network_and_wavelet</t>
-  </si>
-  <si>
     <t>Future Hazard Risks Case Study: Greenland ice sheet mass loss: Potential consequences for mid-latitudes with a focus on the possibility of a tsunami occurrence in Scotland</t>
   </si>
   <si>
@@ -500,13 +383,336 @@
   </si>
   <si>
     <t>Submitted</t>
+  </si>
+  <si>
+    <t>Mohanty, L. K., Sharma, P., Ahmed, R., &amp; Dixit, A.</t>
+  </si>
+  <si>
+    <t>Springer chapter, pp 3–34</t>
+  </si>
+  <si>
+    <t>Journal of Geophysical Research: Atmospheres</t>
+  </si>
+  <si>
+    <r>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>131</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(16), e2026JD046503.</t>
+    </r>
+  </si>
+  <si>
+    <t>Rahimi, S., Huang, L., Thackeray, C. W., Risser, M. D., Tarouilly, E. G., Norris, J., Rhoades, A. M., Bass, B., Hall, A., Lebo, Z. J., Liu, W., Lehner, F., Corrie, T., &amp; Dixit, A.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1029/2026JD046503</t>
+  </si>
+  <si>
+    <t>Dixit, A., Rahimi, S., Huang, L., Musselman, K. N., Vano, J. A., Addor, N., &amp; Lehner, F.</t>
+  </si>
+  <si>
+    <r>
+      <t>21</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color rgb="FF222222"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(5), 054012.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://doi.org/10.1088/1748-9326/ae4113</t>
+  </si>
+  <si>
+    <t>Mohanty, L. K., Gantayat, P., Dixit, A., Das Adhikari, M., Biswas, R., &amp; Singh, V. K.</t>
+  </si>
+  <si>
+    <r>
+      <t>16</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>, 9741.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/s41598-026-35895-7</t>
+  </si>
+  <si>
+    <t>Mohanty, L. K., Tiwari, A., Kumar, A., Singh, V., &amp; Dixit, A.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s11069-025-07888-8</t>
+  </si>
+  <si>
+    <t>Dixit, A., Sahany, S., Mishra, S. K., &amp; Lehner, F.</t>
+  </si>
+  <si>
+    <r>
+      <t>26</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>(3), 345–363.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>122</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>(4)</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://doi.org/10.1175/JHM-D-24-0096.1</t>
+  </si>
+  <si>
+    <t>Mohanty, L. K., Panda, B., Samantaray, S., Dixit, A., &amp; Bhange, S.</t>
+  </si>
+  <si>
+    <r>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>, 363.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s42452-024-05958-3</t>
+  </si>
+  <si>
+    <t>Dixit, A., Sahany, S., &amp; Mishra, S. K.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.jhydrol.2023.130219</t>
+  </si>
+  <si>
+    <t>Dixit, A., Sahany, S., Mishra, S. K., &amp; Mesquita, M. D. S.</t>
+  </si>
+  <si>
+    <r>
+      <t>13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>, 4756.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/s41598-023-31353-w</t>
+  </si>
+  <si>
+    <t>Mohanty, L., Maiti, S., &amp; Dixit, A.</t>
+  </si>
+  <si>
+    <r>
+      <t>10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>, 1038777.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/feart.2022.1038777</t>
+  </si>
+  <si>
+    <t>Dixit, A., Sahany, S., Rajagopalan, B., &amp; Choubey, S.</t>
+  </si>
+  <si>
+    <r>
+      <t>89</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>, 1–14.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://doi.org/10.3354/cr01701</t>
+  </si>
+  <si>
+    <t>Sood, S., Thakur, P. K., Stein, A., Garg, V., &amp; Dixit, A.</t>
+  </si>
+  <si>
+    <r>
+      <t>70</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>(12), 3975–3999.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.asr.2022.10.030</t>
+  </si>
+  <si>
+    <t>Dixit, A., Sahany, S., &amp; Kulkarni, A. V.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.jenvman.2021.113101</t>
+  </si>
+  <si>
+    <t>Dixit, A., &amp; Agarwal, S.</t>
+  </si>
+  <si>
+    <r>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>, 100053.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.acags.2021.100053</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1080/10106049.2020.1844312</t>
+  </si>
+  <si>
+    <r>
+      <t>37</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>(10), 3033–3050.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.rsase.2020.100374</t>
+  </si>
+  <si>
+    <r>
+      <t>20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>, 100374.</t>
+    </r>
+  </si>
+  <si>
+    <t>Aggarwal, S. P., Thakur, P. K., Nikam, B. R., Garg, V., Chouksey, A., Dhote, P. R., Bisht, S., Dixit, A., Arora, S., Choudhury, A., Sharma, V., Chauhan, P., &amp; Kumar, A. S.</t>
+  </si>
+  <si>
+    <r>
+      <t>XLIII-B3-2020</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>, 853–860.</t>
+    </r>
+  </si>
+  <si>
+    <t>https://doi.org/10.5194/isprs-archives-XLIII-B3-2020-853-2020</t>
+  </si>
+  <si>
+    <t>Biased mean states distort mountain climate change through snow-albedo feedbacks</t>
+  </si>
+  <si>
+    <t>Reframing the rarity of extreme low-snow years in the Upper Colorado River Basin</t>
+  </si>
+  <si>
+    <t>Contrasting dynamic and thermodynamic pathways shaped the 2024 Indian heatwave</t>
+  </si>
+  <si>
+    <t>Rahimi, S., Norris, J., Huang, L., Bass, B., Thackeray, C. W., Hall, A., Rhoades, A. M., Risser, M. D., Pierce, D. W., Cayan, D. R., Kalansky, J., Feldman, D., Adhikari, P., Geerts, B., Rasmussen, K. L., Liu, W., Lehner, F., Dixit, A., &amp; Lebo, Z. J.</t>
+  </si>
+  <si>
+    <t>Dixit, A., Najibi, N., Mishra, N., Dixit, J., &amp; Lehner, F.</t>
+  </si>
+  <si>
+    <t>Carr, S., Dixit, A., Lehner, F., Vano, J. A., Addor, N., Petach, T. N., &amp; Musselman, K. N.</t>
+  </si>
+  <si>
+    <t>Role of Earth Observation Data and Hydrological Modeling in Supporting UN SDGs in North West Himalaya.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -517,6 +723,25 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="13"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
     </font>
   </fonts>
   <fills count="3">
@@ -532,7 +757,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -590,11 +815,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -615,6 +853,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -625,24 +872,6 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
         <right/>
         <top style="thin">
           <color indexed="64"/>
@@ -824,6 +1053,24 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
         <vertical style="thin">
           <color indexed="64"/>
         </vertical>
@@ -846,18 +1093,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PublicationsTable" displayName="PublicationsTable" ref="A1:I39" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:I39" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PublicationsTable" displayName="PublicationsTable" ref="A1:I41" totalsRowShown="0" headerRowDxfId="9">
+  <autoFilter ref="A1:I41" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I41">
+    <sortCondition ref="C1:C41"/>
+  </sortState>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Year" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Type" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Type_str" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Title" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Authors" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Venue" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Details" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="URL" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Display" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Year" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Type" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Type_str" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Title" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Authors" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Venue" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Details" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="URL" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Display" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1058,11 +1308,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" style="3" customWidth="1"/>
     <col min="3" max="3" width="15.6640625" style="3" customWidth="1"/>
     <col min="4" max="4" width="54.83203125" style="3" customWidth="1"/>
     <col min="5" max="5" width="38.6640625" style="3" customWidth="1"/>
@@ -1101,1079 +1351,1120 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="85">
-      <c r="A2" s="4">
-        <v>2026</v>
+    <row r="2" spans="1:9" ht="102">
+      <c r="A2" s="4" t="s">
+        <v>120</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>11</v>
+        <v>168</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H2" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="3" spans="1:9" ht="34">
+      <c r="A3" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="68">
-      <c r="A3" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D3" s="4" t="s">
-        <v>19</v>
+        <v>170</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="10"/>
+    </row>
+    <row r="4" spans="1:9" ht="34">
+      <c r="A4" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="85">
-      <c r="A4" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D4" s="4" t="s">
-        <v>24</v>
+        <v>169</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="51">
+        <v>173</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="10"/>
+    </row>
+    <row r="5" spans="1:9" ht="68">
       <c r="A5" s="4">
         <v>2026</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>31</v>
+        <v>125</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>123</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>22</v>
+        <v>124</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>32</v>
+        <v>126</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="68">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="34">
       <c r="A6" s="4">
         <v>2026</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="34">
+      <c r="A7" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="4" t="s">
+      <c r="E7" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="34">
+      <c r="A8" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="85">
-      <c r="A7" s="4">
+      <c r="D8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="34">
+      <c r="A9" s="4">
         <v>2025</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="I7" s="4" t="s">
+      <c r="B9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="85">
-      <c r="A8" s="4">
-        <v>2024</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="68">
-      <c r="A9" s="4">
-        <v>2024</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D9" s="4" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>49</v>
+        <v>135</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>22</v>
+        <v>136</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="85">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="34">
       <c r="A10" s="4">
         <v>2024</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="4"/>
       <c r="G10" s="4" t="s">
-        <v>52</v>
+        <v>140</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>53</v>
+        <v>141</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="85">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="51">
       <c r="A11" s="4">
         <v>2023</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>57</v>
+        <v>35</v>
+      </c>
+      <c r="E11" t="s">
+        <v>142</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>37</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>59</v>
+        <v>143</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="68">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="34">
       <c r="A12" s="4">
         <v>2023</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>21</v>
-      </c>
       <c r="G12" s="4" t="s">
-        <v>62</v>
+        <v>145</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>63</v>
+        <v>146</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="85">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="34">
       <c r="A13" s="4">
         <v>2023</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>66</v>
+        <v>147</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>41</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>22</v>
+        <v>148</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>67</v>
+        <v>149</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="51">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="34">
       <c r="A14" s="4">
         <v>2022</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="51">
+      <c r="A15" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="34">
+      <c r="A16" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="34">
+      <c r="A17" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="34">
+      <c r="A18" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="68">
+      <c r="A19" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="34">
+      <c r="A20" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="85">
+      <c r="A21" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="H14" s="4" t="s">
+      <c r="C21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="51">
+      <c r="A22" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="I14" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="68">
-      <c r="A15" s="4">
-        <v>2022</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="C22" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="D22" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="E22" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="H15" s="4" t="s">
+      <c r="F22" s="2"/>
+      <c r="G22" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="85">
-      <c r="A16" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="I22" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="51">
+      <c r="A23" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="85">
-      <c r="A17" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="68">
-      <c r="A18" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="51">
-      <c r="A19" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="I23" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="85">
+      <c r="A24" s="2">
+        <v>2016</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="G24" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="I24" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="68">
+      <c r="A25" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="I19" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="68">
-      <c r="A20" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="68">
-      <c r="A21" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="85">
-      <c r="A22" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="85">
-      <c r="A23" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="102">
-      <c r="A24" s="2">
-        <v>2019</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="204">
-      <c r="A25" s="2">
-        <v>2019</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="51">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="85">
       <c r="A26" s="2">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="51">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="68">
       <c r="A27" s="2">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="34">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="85">
       <c r="A28" s="2">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="85">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="68">
       <c r="A29" s="2">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="68">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="51">
       <c r="A30" s="2">
         <v>2015</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F30" s="2"/>
+        <v>107</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="G30" s="2" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="85">
       <c r="A31" s="2">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="68">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="85">
       <c r="A32" s="2">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>136</v>
+        <v>61</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>112</v>
+        <v>73</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="85">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="34">
       <c r="A33" s="2">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>111</v>
+        <v>9</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="68">
-      <c r="A34" s="2">
-        <v>2015</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>111</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="85">
+      <c r="A34" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="51">
+        <v>27</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="85">
       <c r="A35" s="2">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>111</v>
+        <v>51</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>112</v>
+        <v>51</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>145</v>
+        <v>52</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>147</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
-        <v>148</v>
+        <v>53</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>149</v>
+        <v>54</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="68">
       <c r="A36" s="2">
-        <v>2014</v>
+        <v>2022</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>9</v>
+        <v>51</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>150</v>
+        <v>51</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>151</v>
+        <v>55</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
-        <v>152</v>
+        <v>53</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>153</v>
+        <v>56</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="85">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="102">
       <c r="A37" s="2">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>111</v>
+        <v>15</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>154</v>
+        <v>68</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
-        <v>155</v>
+        <v>70</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>156</v>
+        <v>71</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="85">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="51">
       <c r="A38" s="2">
-        <v>2013</v>
+        <v>2019</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>157</v>
+        <v>77</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>92</v>
+        <v>29</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="85">
+      <c r="A39" s="2">
+        <v>2014</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="51">
+      <c r="A40" s="4">
+        <v>2022</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="68">
+      <c r="A41" s="5">
+        <v>2014</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D41" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="85">
-      <c r="A39" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="I39" s="7" t="s">
-        <v>16</v>
+      <c r="E41" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="B2:B39" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="B2:B41" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Articles,Presentation,Poster,Reports/Chapter,Seminar/Invited talk"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H17" r:id="rId1" xr:uid="{BDF92706-657D-D349-9948-227810B878A1}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ankurdixit/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC494A1-1B9C-3943-86F8-2B1625CB4040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DCD0F6B-9BA2-844D-9874-FAA31161878A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="20120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -382,9 +382,6 @@
     <t>https://www.researchgate.net/publication/261458672_Comparison_of_various_models_and_optimum_range_of_its_parameters_used_in_SVM_classification_of_digital_satellite_image</t>
   </si>
   <si>
-    <t>Submitted</t>
-  </si>
-  <si>
     <t>Mohanty, L. K., Sharma, P., Ahmed, R., &amp; Dixit, A.</t>
   </si>
   <si>
@@ -706,6 +703,9 @@
   </si>
   <si>
     <t>Role of Earth Observation Data and Hydrological Modeling in Supporting UN SDGs in North West Himalaya.</t>
+  </si>
+  <si>
+    <t>submitted</t>
   </si>
 </sst>
 </file>
@@ -1353,7 +1353,7 @@
     </row>
     <row r="2" spans="1:9" ht="102">
       <c r="A2" s="4" t="s">
-        <v>120</v>
+        <v>174</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>15</v>
@@ -1362,10 +1362,10 @@
         <v>16</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -1374,7 +1374,7 @@
     </row>
     <row r="3" spans="1:9" ht="34">
       <c r="A3" s="4" t="s">
-        <v>120</v>
+        <v>174</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>15</v>
@@ -1383,10 +1383,10 @@
         <v>16</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
@@ -1395,7 +1395,7 @@
     </row>
     <row r="4" spans="1:9" ht="34">
       <c r="A4" s="4" t="s">
-        <v>120</v>
+        <v>174</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>15</v>
@@ -1404,10 +1404,10 @@
         <v>16</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -1428,16 +1428,16 @@
         <v>24</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>125</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>126</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>14</v>
@@ -1457,16 +1457,16 @@
         <v>19</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>20</v>
       </c>
       <c r="G6" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>14</v>
@@ -1486,16 +1486,16 @@
         <v>17</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>18</v>
       </c>
       <c r="G7" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>132</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>14</v>
@@ -1515,16 +1515,16 @@
         <v>21</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>22</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>14</v>
@@ -1544,16 +1544,16 @@
         <v>25</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>14</v>
@@ -1573,16 +1573,16 @@
         <v>32</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>33</v>
       </c>
       <c r="G10" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>140</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>141</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>14</v>
@@ -1602,7 +1602,7 @@
         <v>35</v>
       </c>
       <c r="E11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>37</v>
@@ -1611,7 +1611,7 @@
         <v>38</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>14</v>
@@ -1631,16 +1631,16 @@
         <v>39</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>18</v>
       </c>
       <c r="G12" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>146</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>14</v>
@@ -1660,16 +1660,16 @@
         <v>40</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>41</v>
       </c>
       <c r="G13" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>149</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>14</v>
@@ -1689,16 +1689,16 @@
         <v>47</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>48</v>
       </c>
       <c r="G14" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>151</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>152</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>14</v>
@@ -1718,16 +1718,16 @@
         <v>49</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>50</v>
       </c>
       <c r="G15" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>155</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>14</v>
@@ -1747,7 +1747,7 @@
         <v>57</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>58</v>
@@ -1756,7 +1756,7 @@
         <v>59</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>14</v>
@@ -1776,16 +1776,16 @@
         <v>60</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>62</v>
       </c>
       <c r="G17" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>159</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>160</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>14</v>
@@ -1805,16 +1805,16 @@
         <v>63</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>64</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>14</v>
@@ -1831,19 +1831,19 @@
         <v>16</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>65</v>
       </c>
       <c r="G19" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="H19" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>167</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>14</v>
@@ -1863,16 +1863,16 @@
         <v>66</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>67</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>14</v>
@@ -1892,13 +1892,13 @@
         <v>11</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>12</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>13</v>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ankurdixit/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DCD0F6B-9BA2-844D-9874-FAA31161878A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19465128-2BFE-3648-BCF1-1D6CA8FC509A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="20120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="176">
   <si>
     <t>Year</t>
   </si>
@@ -706,6 +706,9 @@
   </si>
   <si>
     <t>submitted</t>
+  </si>
+  <si>
+    <t>Submitted</t>
   </si>
 </sst>
 </file>
@@ -1356,7 +1359,7 @@
         <v>174</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>15</v>
+        <v>175</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>16</v>
@@ -1377,7 +1380,7 @@
         <v>174</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>15</v>
+        <v>175</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>16</v>
@@ -1398,7 +1401,7 @@
         <v>174</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>175</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>16</v>
@@ -2454,7 +2457,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" sqref="B2:B41" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Articles,Presentation,Poster,Reports/Chapter,Seminar/Invited talk"</formula1>
     </dataValidation>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ankurdixit/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19465128-2BFE-3648-BCF1-1D6CA8FC509A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282854ED-D548-344E-B2AB-B1B5F25F3B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="20120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="174">
   <si>
     <t>Year</t>
   </si>
@@ -122,9 +122,6 @@
   </si>
   <si>
     <t>Discover Applied Sciences</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
   <si>
     <t>Modeling the Climate Change Impact on Hydroclimate Fluxes over the Beas Basin using a High-Resolution Glacier-Atmosphere-Hydrology Coupled Setup</t>
@@ -706,9 +703,6 @@
   </si>
   <si>
     <t>submitted</t>
-  </si>
-  <si>
-    <t>Submitted</t>
   </si>
 </sst>
 </file>
@@ -760,7 +754,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -818,24 +812,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -860,9 +841,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1356,66 +1334,72 @@
     </row>
     <row r="2" spans="1:9" ht="102">
       <c r="A2" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>175</v>
+        <v>15</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
+      <c r="I2" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="3" spans="1:9" ht="34">
       <c r="A3" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>175</v>
+        <v>15</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="10"/>
+      <c r="I3" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="4" spans="1:9" ht="34">
       <c r="A4" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>175</v>
+        <v>15</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="10"/>
+      <c r="I4" s="4" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="68">
       <c r="A5" s="4">
@@ -1431,16 +1415,16 @@
         <v>24</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>125</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>14</v>
@@ -1460,16 +1444,16 @@
         <v>19</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>20</v>
       </c>
       <c r="G6" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>128</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>14</v>
@@ -1489,16 +1473,16 @@
         <v>17</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>18</v>
       </c>
       <c r="G7" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>14</v>
@@ -1518,16 +1502,16 @@
         <v>21</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>22</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>14</v>
@@ -1547,16 +1531,16 @@
         <v>25</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>14</v>
@@ -1576,16 +1560,16 @@
         <v>32</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>33</v>
       </c>
       <c r="G10" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>140</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>14</v>
@@ -1602,19 +1586,19 @@
         <v>16</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E11" t="s">
+        <v>140</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>141</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>142</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>14</v>
@@ -1631,19 +1615,19 @@
         <v>16</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>18</v>
       </c>
       <c r="G12" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="H12" s="4" t="s">
         <v>144</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>145</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>14</v>
@@ -1660,19 +1644,19 @@
         <v>16</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="F13" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" s="4" t="s">
+      <c r="H13" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>148</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>14</v>
@@ -1689,19 +1673,19 @@
         <v>16</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="F14" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="G14" s="4" t="s">
+      <c r="H14" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>151</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>14</v>
@@ -1718,19 +1702,19 @@
         <v>16</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="F15" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="F15" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="G15" s="4" t="s">
+      <c r="H15" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>154</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>14</v>
@@ -1747,19 +1731,19 @@
         <v>16</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F16" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="G16" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>156</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>14</v>
@@ -1776,19 +1760,19 @@
         <v>16</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="F17" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="G17" s="4" t="s">
+      <c r="H17" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>159</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>14</v>
@@ -1805,19 +1789,19 @@
         <v>16</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F18" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>64</v>
-      </c>
       <c r="G18" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>14</v>
@@ -1834,19 +1818,19 @@
         <v>16</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E19" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="F19" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="G19" s="4" t="s">
+      <c r="H19" s="4" t="s">
         <v>165</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>166</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>14</v>
@@ -1863,19 +1847,19 @@
         <v>16</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F20" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>67</v>
-      </c>
       <c r="G20" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>14</v>
@@ -1895,13 +1879,13 @@
         <v>11</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>12</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>13</v>
@@ -1915,23 +1899,23 @@
         <v>2019</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>14</v>
@@ -1942,23 +1926,23 @@
         <v>2019</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="D23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>14</v>
@@ -1969,25 +1953,25 @@
         <v>2016</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="D24" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="G24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>14</v>
@@ -1998,23 +1982,23 @@
         <v>2015</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="D25" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>14</v>
@@ -2025,23 +2009,23 @@
         <v>2015</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="D26" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>94</v>
       </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>14</v>
@@ -2052,23 +2036,23 @@
         <v>2015</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="D27" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>14</v>
@@ -2079,23 +2063,23 @@
         <v>2015</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="D28" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>14</v>
@@ -2106,25 +2090,25 @@
         <v>2015</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="D29" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F29" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="H29" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>14</v>
@@ -2135,25 +2119,25 @@
         <v>2015</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="D30" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="G30" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="H30" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>14</v>
@@ -2164,23 +2148,23 @@
         <v>2013</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="D31" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>14</v>
@@ -2191,23 +2175,23 @@
         <v>2013</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="D32" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>14</v>
@@ -2221,20 +2205,20 @@
         <v>9</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="E33" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>14</v>
@@ -2272,23 +2256,23 @@
         <v>2022</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="E35" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>14</v>
@@ -2299,23 +2283,23 @@
         <v>2022</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>14</v>
@@ -2332,17 +2316,17 @@
         <v>23</v>
       </c>
       <c r="D37" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H37" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>14</v>
@@ -2353,23 +2337,23 @@
         <v>2019</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>29</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>14</v>
@@ -2380,23 +2364,23 @@
         <v>2014</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>29</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H39" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>14</v>
@@ -2410,23 +2394,23 @@
         <v>9</v>
       </c>
       <c r="C40" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="E40" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="F40" s="4"/>
       <c r="G40" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H40" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="H40" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="I40" s="4" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:9" ht="68">
@@ -2437,27 +2421,27 @@
         <v>9</v>
       </c>
       <c r="C41" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D41" s="6" t="s">
         <v>111</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>112</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>29</v>
       </c>
       <c r="F41" s="6"/>
       <c r="G41" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H41" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="H41" s="6" t="s">
-        <v>114</v>
-      </c>
       <c r="I41" s="7" t="s">
         <v>14</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" sqref="B2:B41" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Articles,Presentation,Poster,Reports/Chapter,Seminar/Invited talk"</formula1>
     </dataValidation>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ankurdixit/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282854ED-D548-344E-B2AB-B1B5F25F3B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3ABF37E-1F66-0D40-A7BE-5E65EAA857A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="20120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -702,7 +702,7 @@
     <t>Role of Earth Observation Data and Hydrological Modeling in Supporting UN SDGs in North West Himalaya.</t>
   </si>
   <si>
-    <t>submitted</t>
+    <t>Submitted</t>
   </si>
 </sst>
 </file>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ankurdixit/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3ABF37E-1F66-0D40-A7BE-5E65EAA857A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8675729C-F21B-184E-BC81-34E4D6DEF77E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="20120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -693,9 +693,6 @@
     <t>Rahimi, S., Norris, J., Huang, L., Bass, B., Thackeray, C. W., Hall, A., Rhoades, A. M., Risser, M. D., Pierce, D. W., Cayan, D. R., Kalansky, J., Feldman, D., Adhikari, P., Geerts, B., Rasmussen, K. L., Liu, W., Lehner, F., Dixit, A., &amp; Lebo, Z. J.</t>
   </si>
   <si>
-    <t>Dixit, A., Najibi, N., Mishra, N., Dixit, J., &amp; Lehner, F.</t>
-  </si>
-  <si>
     <t>Carr, S., Dixit, A., Lehner, F., Vano, J. A., Addor, N., Petach, T. N., &amp; Musselman, K. N.</t>
   </si>
   <si>
@@ -703,13 +700,35 @@
   </si>
   <si>
     <t>Submitted</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Dixit, A., Najibi, N., Mishra, N., </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>Dixit, A.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>, &amp; Lehner, F.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -736,6 +755,12 @@
     </font>
     <font>
       <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -1332,9 +1357,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="102">
+    <row r="2" spans="1:9" ht="34">
       <c r="A2" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>15</v>
@@ -1343,10 +1368,10 @@
         <v>16</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
@@ -1357,7 +1382,7 @@
     </row>
     <row r="3" spans="1:9" ht="34">
       <c r="A3" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>15</v>
@@ -1366,7 +1391,7 @@
         <v>16</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>170</v>
@@ -1378,9 +1403,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="34">
+    <row r="4" spans="1:9" ht="102">
       <c r="A4" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>15</v>
@@ -1389,10 +1414,10 @@
         <v>16</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -1818,7 +1843,7 @@
         <v>16</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>163</v>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ankurdixit/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8675729C-F21B-184E-BC81-34E4D6DEF77E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B246D2-FFAD-EB45-9DE6-ED38117FF396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="20120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="175">
   <si>
     <t>Year</t>
   </si>
@@ -722,6 +722,9 @@
       </rPr>
       <t>, &amp; Lehner, F.</t>
     </r>
+  </si>
+  <si>
+    <t>Column1</t>
   </si>
 </sst>
 </file>
@@ -779,7 +782,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -837,11 +840,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -868,11 +895,38 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="11">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1099,21 +1153,22 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PublicationsTable" displayName="PublicationsTable" ref="A1:I41" totalsRowShown="0" headerRowDxfId="9">
-  <autoFilter ref="A1:I41" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PublicationsTable" displayName="PublicationsTable" ref="A1:J41" totalsRowShown="0" headerRowDxfId="10">
+  <autoFilter ref="A1:J41" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I41">
     <sortCondition ref="C1:C41"/>
   </sortState>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Year" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Type" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Type_str" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Title" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Authors" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Venue" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Details" dataDxfId="2"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="URL" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Display" dataDxfId="0"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Year" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Type" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Type_str" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Title" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Authors" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Venue" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Details" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="URL" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Display" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{3A4134C7-5046-6849-9C60-A6A6D074382D}" name="Column1" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1314,7 +1369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="3" customWidth="1"/>
@@ -1328,7 +1383,7 @@
     <col min="9" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17">
+    <row r="1" spans="1:10" ht="17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1356,36 +1411,42 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="34">
+      <c r="J1" s="12" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="34">
       <c r="A2" s="4" t="s">
         <v>172</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="34">
+      <c r="I2" s="4"/>
+      <c r="J2" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="34">
       <c r="A3" s="4" t="s">
         <v>172</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>15</v>
+        <v>172</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>16</v>
@@ -1403,12 +1464,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="102">
+    <row r="4" spans="1:10" ht="102">
       <c r="A4" s="4" t="s">
         <v>172</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>172</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>16</v>
@@ -1426,7 +1487,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="68">
+    <row r="5" spans="1:10" ht="68">
       <c r="A5" s="4">
         <v>2026</v>
       </c>
@@ -1455,7 +1516,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="34">
+    <row r="6" spans="1:10" ht="34">
       <c r="A6" s="4">
         <v>2026</v>
       </c>
@@ -1484,7 +1545,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="34">
+    <row r="7" spans="1:10" ht="34">
       <c r="A7" s="4">
         <v>2026</v>
       </c>
@@ -1513,7 +1574,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="34">
+    <row r="8" spans="1:10" ht="34">
       <c r="A8" s="4">
         <v>2026</v>
       </c>
@@ -1542,7 +1603,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="34">
+    <row r="9" spans="1:10" ht="34">
       <c r="A9" s="4">
         <v>2025</v>
       </c>
@@ -1571,7 +1632,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="34">
+    <row r="10" spans="1:10" ht="34">
       <c r="A10" s="4">
         <v>2024</v>
       </c>
@@ -1600,7 +1661,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="51">
+    <row r="11" spans="1:10" ht="51">
       <c r="A11" s="4">
         <v>2023</v>
       </c>
@@ -1629,7 +1690,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="34">
+    <row r="12" spans="1:10" ht="34">
       <c r="A12" s="4">
         <v>2023</v>
       </c>
@@ -1658,7 +1719,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="34">
+    <row r="13" spans="1:10" ht="34">
       <c r="A13" s="4">
         <v>2023</v>
       </c>
@@ -1687,7 +1748,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="34">
+    <row r="14" spans="1:10" ht="34">
       <c r="A14" s="4">
         <v>2022</v>
       </c>
@@ -1716,7 +1777,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="51">
+    <row r="15" spans="1:10" ht="51">
       <c r="A15" s="2">
         <v>2022</v>
       </c>
@@ -1745,7 +1806,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="34">
+    <row r="16" spans="1:10" ht="34">
       <c r="A16" s="2">
         <v>2021</v>
       </c>
@@ -2222,7 +2283,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="34">
+    <row r="33" spans="1:10" ht="34">
       <c r="A33" s="2">
         <v>2016</v>
       </c>
@@ -2249,7 +2310,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="85">
+    <row r="34" spans="1:10" ht="85">
       <c r="A34" s="4">
         <v>2024</v>
       </c>
@@ -2276,7 +2337,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="85">
+    <row r="35" spans="1:10" ht="85">
       <c r="A35" s="2">
         <v>2022</v>
       </c>
@@ -2303,7 +2364,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="68">
+    <row r="36" spans="1:10" ht="68">
       <c r="A36" s="2">
         <v>2022</v>
       </c>
@@ -2330,7 +2391,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="102">
+    <row r="37" spans="1:10" ht="102">
       <c r="A37" s="2">
         <v>2019</v>
       </c>
@@ -2357,7 +2418,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="51">
+    <row r="38" spans="1:10" ht="51">
       <c r="A38" s="2">
         <v>2019</v>
       </c>
@@ -2384,7 +2445,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="85">
+    <row r="39" spans="1:10" ht="85">
       <c r="A39" s="2">
         <v>2014</v>
       </c>
@@ -2411,7 +2472,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="51">
+    <row r="40" spans="1:10" ht="51">
       <c r="A40" s="4">
         <v>2022</v>
       </c>
@@ -2438,7 +2499,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="68">
+    <row r="41" spans="1:10" ht="68">
       <c r="A41" s="5">
         <v>2014</v>
       </c>
@@ -2464,10 +2525,11 @@
       <c r="I41" s="7" t="s">
         <v>14</v>
       </c>
+      <c r="J41" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="B2:B41" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="C2 B5:B41" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Articles,Presentation,Poster,Reports/Chapter,Seminar/Invited talk"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ankurdixit/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B246D2-FFAD-EB45-9DE6-ED38117FF396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA91C1BD-1491-0A4C-9C37-44B5DE19E81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="20120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="175">
   <si>
     <t>Year</t>
   </si>
@@ -868,7 +868,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -900,6 +900,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1426,20 +1427,18 @@
         <v>15</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>16</v>
+        <v>168</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="F2" s="4" t="s">
         <v>173</v>
       </c>
+      <c r="F2" s="13"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="10" t="s">
-        <v>14</v>
-      </c>
+      <c r="I2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="13"/>
     </row>
     <row r="3" spans="1:10" ht="34">
       <c r="A3" s="4" t="s">

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ankurdixit/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA91C1BD-1491-0A4C-9C37-44B5DE19E81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D29307-8F04-8C46-BBC3-848B8D66A14E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="20120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="174">
   <si>
     <t>Year</t>
   </si>
@@ -702,36 +702,14 @@
     <t>Submitted</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Dixit, A., Najibi, N., Mishra, N., </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>Dixit, A.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>, &amp; Lehner, F.</t>
-    </r>
-  </si>
-  <si>
-    <t>Column1</t>
+    <t>Dixit, A., Najibi, N., Mishra, N., Dixit, A., &amp; Lehner, F.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -762,12 +740,6 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -782,7 +754,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -854,21 +826,36 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right/>
+      <top style="thin">
         <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -898,36 +885,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -1154,22 +1126,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PublicationsTable" displayName="PublicationsTable" ref="A1:J41" totalsRowShown="0" headerRowDxfId="10">
-  <autoFilter ref="A1:J41" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I41">
-    <sortCondition ref="C1:C41"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PublicationsTable" displayName="PublicationsTable" ref="A1:I48" totalsRowShown="0" headerRowDxfId="9">
+  <autoFilter ref="A1:I48" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I48">
+    <sortCondition ref="C1:C48"/>
   </sortState>
-  <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Year" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Type" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Type_str" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Title" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Authors" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Venue" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Details" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="URL" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Display" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{3A4134C7-5046-6849-9C60-A6A6D074382D}" name="Column1" dataDxfId="0"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Year" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Type" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Type_str" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Title" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Authors" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Venue" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Details" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="URL" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Display" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1370,7 +1341,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="3" customWidth="1"/>
@@ -1384,7 +1355,7 @@
     <col min="9" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17">
+    <row r="1" spans="1:9" ht="17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1412,286 +1383,149 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="12" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="34">
-      <c r="A2" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="F2" s="13"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="11"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="13"/>
-    </row>
-    <row r="3" spans="1:10" ht="34">
-      <c r="A3" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>170</v>
-      </c>
-      <c r="F3" s="4"/>
+      <c r="I2" s="10"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="12"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="102">
-      <c r="A4" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="F4" s="4"/>
+      <c r="I3" s="13"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="12"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="68">
-      <c r="A5" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="I4" s="13"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="12"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="13"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="12"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="13"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="12"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="13"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="12"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="13"/>
+    </row>
+    <row r="9" spans="1:9" ht="34">
+      <c r="A9" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="34">
-      <c r="A6" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="34">
-      <c r="A7" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="34">
-      <c r="A8" s="4">
-        <v>2026</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="34">
-      <c r="A9" s="4">
-        <v>2025</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="D9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="34">
-      <c r="A10" s="4">
-        <v>2024</v>
+        <v>168</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="34">
+      <c r="A10" s="4" t="s">
+        <v>172</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>15</v>
+        <v>172</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>32</v>
+        <v>167</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>139</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
       <c r="I10" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="51">
-      <c r="A11" s="4">
-        <v>2023</v>
+    <row r="11" spans="1:9" ht="102">
+      <c r="A11" s="4" t="s">
+        <v>172</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>15</v>
+        <v>172</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" t="s">
-        <v>140</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>141</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
       <c r="I11" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="34">
+    <row r="12" spans="1:9" ht="68">
       <c r="A12" s="4">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>15</v>
@@ -1700,27 +1534,27 @@
         <v>16</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>18</v>
+        <v>123</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>121</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="34">
+    <row r="13" spans="1:9" ht="34">
       <c r="A13" s="4">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>15</v>
@@ -1729,27 +1563,27 @@
         <v>16</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="F13" s="9" t="s">
-        <v>40</v>
+        <v>125</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="34">
+    <row r="14" spans="1:9" ht="34">
       <c r="A14" s="4">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>15</v>
@@ -1758,222 +1592,222 @@
         <v>16</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="51">
-      <c r="A15" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B15" s="2" t="s">
+    <row r="15" spans="1:9" ht="34">
+      <c r="A15" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>48</v>
+      <c r="D15" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>152</v>
+        <v>135</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="34">
-      <c r="A16" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B16" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="34">
+      <c r="A16" s="4">
+        <v>2025</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>56</v>
+      <c r="D16" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="I16" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="I16" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="34">
-      <c r="A17" s="2">
-        <v>2021</v>
-      </c>
-      <c r="B17" s="2" t="s">
+      <c r="A17" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>59</v>
+      <c r="D17" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="34">
-      <c r="A18" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B18" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="51">
+      <c r="A18" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>156</v>
+      <c r="D18" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" t="s">
+        <v>140</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>160</v>
+        <v>37</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="68">
-      <c r="A19" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B19" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="34">
+      <c r="A19" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>171</v>
+      <c r="D19" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="I19" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I19" s="4" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="34">
-      <c r="A20" s="2">
-        <v>2020</v>
-      </c>
-      <c r="B20" s="2" t="s">
+      <c r="A20" s="4">
+        <v>2023</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>65</v>
+      <c r="D20" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="85">
+        <v>147</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="34">
       <c r="A21" s="4">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>15</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>12</v>
+        <v>148</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>47</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>13</v>
+        <v>150</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>14</v>
@@ -1981,198 +1815,210 @@
     </row>
     <row r="22" spans="1:9" ht="51">
       <c r="A22" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="34">
+      <c r="A23" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="34">
+      <c r="A24" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="34">
+      <c r="A25" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="68">
+      <c r="A26" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="34">
+      <c r="A27" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="85">
+      <c r="A28" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="51">
+      <c r="A29" s="2">
         <v>2019</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="51">
-      <c r="A23" s="2">
-        <v>2019</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="85">
-      <c r="A24" s="2">
-        <v>2016</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="68">
-      <c r="A25" s="2">
-        <v>2015</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="85">
-      <c r="A26" s="2">
-        <v>2015</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="68">
-      <c r="A27" s="2">
-        <v>2015</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="85">
-      <c r="A28" s="2">
-        <v>2015</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="68">
-      <c r="A29" s="2">
-        <v>2015</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>71</v>
@@ -2181,19 +2027,17 @@
         <v>72</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>102</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="F29" s="2"/>
       <c r="G29" s="2" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>14</v>
@@ -2201,7 +2045,7 @@
     </row>
     <row r="30" spans="1:9" ht="51">
       <c r="A30" s="2">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>71</v>
@@ -2210,19 +2054,17 @@
         <v>72</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>107</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="F30" s="2"/>
       <c r="G30" s="2" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>14</v>
@@ -2230,7 +2072,7 @@
     </row>
     <row r="31" spans="1:9" ht="85">
       <c r="A31" s="2">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>71</v>
@@ -2239,25 +2081,27 @@
         <v>72</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F31" s="2"/>
+        <v>86</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="G31" s="2" t="s">
         <v>72</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="85">
+    <row r="32" spans="1:9" ht="68">
       <c r="A32" s="2">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>71</v>
@@ -2266,274 +2110,466 @@
         <v>72</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2" t="s">
         <v>72</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="34">
+    <row r="33" spans="1:9" ht="85">
       <c r="A33" s="2">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="85">
-      <c r="A34" s="4">
-        <v>2024</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>9</v>
+    <row r="34" spans="1:9" ht="68">
+      <c r="A34" s="2">
+        <v>2015</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>71</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I34" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="85">
+        <v>72</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="85">
       <c r="A35" s="2">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>35</v>
+        <v>99</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>53</v>
+        <v>100</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="68">
+    <row r="36" spans="1:9" ht="68">
       <c r="A36" s="2">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>54</v>
+        <v>101</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F36" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>102</v>
+      </c>
       <c r="G36" s="2" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="I36" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="102">
+    <row r="37" spans="1:9" ht="51">
       <c r="A37" s="2">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>15</v>
+        <v>71</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F37" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>107</v>
+      </c>
       <c r="G37" s="2" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="51">
+    <row r="38" spans="1:9" ht="85">
       <c r="A38" s="2">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="85">
+    <row r="39" spans="1:9" ht="85">
       <c r="A39" s="2">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>71</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="F39" s="2"/>
       <c r="G39" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="34">
+      <c r="A40" s="2">
+        <v>2016</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="85">
+      <c r="A41" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I41" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="85">
+      <c r="A42" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="68">
+      <c r="A43" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="102">
+      <c r="A44" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="51">
+      <c r="A45" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="85">
+      <c r="A46" s="2">
+        <v>2014</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="H39" s="2" t="s">
+      <c r="H46" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="I39" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="51">
-      <c r="A40" s="4">
+      <c r="I46" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="51">
+      <c r="A47" s="4">
         <v>2022</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B47" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D47" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E47" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4" t="s">
+      <c r="F47" s="4"/>
+      <c r="G47" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H40" s="4" t="s">
+      <c r="H47" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="I40" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" ht="68">
-      <c r="A41" s="5">
+      <c r="I47" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="68">
+      <c r="A48" s="5">
         <v>2014</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B48" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C41" s="6" t="s">
+      <c r="C48" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D48" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E48" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F41" s="6"/>
-      <c r="G41" s="6" t="s">
+      <c r="F48" s="6"/>
+      <c r="G48" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="H41" s="6" t="s">
+      <c r="H48" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="I41" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J41" s="11"/>
+      <c r="I48" s="7" t="s">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="C2 B5:B41" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="B12:B48 C2:C9" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Articles,Presentation,Poster,Reports/Chapter,Seminar/Invited talk"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="H17" r:id="rId1" xr:uid="{BDF92706-657D-D349-9948-227810B878A1}"/>
+    <hyperlink ref="H24" r:id="rId1" xr:uid="{BDF92706-657D-D349-9948-227810B878A1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ankurdixit/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60D29307-8F04-8C46-BBC3-848B8D66A14E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4EBA82-6315-FA47-8B5E-75C8D4DF8E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="20120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -855,7 +855,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -890,9 +890,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1463,12 +1460,12 @@
         <v>172</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="4" t="s">
         <v>173</v>
       </c>
       <c r="G9" s="4"/>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ankurdixit/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4EBA82-6315-FA47-8B5E-75C8D4DF8E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D880BA5A-0B72-8D47-9915-68F92DAA0C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="20120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3340" yWindow="1200" windowWidth="38400" windowHeight="20120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Publications" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="160">
   <si>
     <t>Year</t>
   </si>
@@ -61,9 +61,6 @@
     <t>Climate Change, Water Resources, and Natural Hazards in the Himalayas</t>
   </si>
   <si>
-    <t>https://www.researchgate.net/publication/411981482_Cryospheric_Processes_Responsible_for_Lake_Formation_A_Review_on_Lake_Types_Threats_Status_and_Their_Distribution_within_the_Himalaya</t>
-  </si>
-  <si>
     <t>Yes</t>
   </si>
   <si>
@@ -91,9 +88,6 @@
     <t>Natural Hazards</t>
   </si>
   <si>
-    <t>Preprint</t>
-  </si>
-  <si>
     <t>Bias correction choices strongly shape California's projected megaflood risk</t>
   </si>
   <si>
@@ -103,21 +97,9 @@
     <t>Journal of Hydrometeorology</t>
   </si>
   <si>
-    <t>Dataset / method</t>
-  </si>
-  <si>
-    <t>WRF-Hydro and PEST files for calibration over Beas Basin</t>
-  </si>
-  <si>
     <t>Ankur Dixit</t>
   </si>
   <si>
-    <t>Dataset / method · Zenodo record 13830819</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/384288527_WRF-Hydro_and_PEST_files_for_calibration_over_Beas_Basin_Files_at_-_httpszenodoorgrecords13830819</t>
-  </si>
-  <si>
     <t>Analyzing water level variability in Odisha: insights from multi-year data and spatial analysis</t>
   </si>
   <si>
@@ -127,9 +109,6 @@
     <t>Modeling the Climate Change Impact on Hydroclimate Fluxes over the Beas Basin using a High-Resolution Glacier-Atmosphere-Hydrology Coupled Setup</t>
   </si>
   <si>
-    <t>Ankur Dixit, Sandeep Sahany, Saroj Kanta Mishra</t>
-  </si>
-  <si>
     <t>Journal of Hydrology</t>
   </si>
   <si>
@@ -145,21 +124,6 @@
     <t>Frontiers in Earth Science</t>
   </si>
   <si>
-    <t>Supplementary data</t>
-  </si>
-  <si>
-    <t>1-s2.0-S0273117722009681-mmc1.docx</t>
-  </si>
-  <si>
-    <t>Sahil Sood, Praveen K. Thakur, Alfred Stein, et al., Ankur Dixit</t>
-  </si>
-  <si>
-    <t>Supplementary data for Samudra Tapu glacier article</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/364819698_1-s20-S0273117722009681-mmc1docx</t>
-  </si>
-  <si>
     <t>Role of changing land use and land cover (LULC) on the 2018 megafloods over Kerala, India</t>
   </si>
   <si>
@@ -178,18 +142,9 @@
     <t>The climate change impact on the future water availability over the Beas basin using high-resolution coupled glacier-atmosphere-hydrology modeling setup</t>
   </si>
   <si>
-    <t>FIHM / AGU poster</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/361724010_The_climate_change_impact_on_the_future_water_availability_over_the_Beas_basin_using_high-resolution_coupled_glacier-atmosphere-hydrology_modeling_setup</t>
-  </si>
-  <si>
     <t>Calibration and parameter sensitivity of WRF-Hydro over Beas basin using parallel PEST</t>
   </si>
   <si>
-    <t>https://www.researchgate.net/publication/361723815_Calibration_and_parameter_sensitivity_of_WRF-Hydro_over_Beas_basin_using_parallel_PEST</t>
-  </si>
-  <si>
     <t>Glacial changes over the Himalayan Beas basin under global warming</t>
   </si>
   <si>
@@ -202,9 +157,6 @@
     <t>Non-linear Spectral Unmixing of Hyperspectral Data using Modified PPNMM</t>
   </si>
   <si>
-    <t>Ankur Dixit, Shefali Agarwal</t>
-  </si>
-  <si>
     <t>Applied Computing and Geosciences</t>
   </si>
   <si>
@@ -226,157 +178,43 @@
     <t>Future Hazard Risks Case Study: Greenland ice sheet mass loss: Potential consequences for mid-latitudes with a focus on the possibility of a tsunami occurrence in Scotland</t>
   </si>
   <si>
-    <t>Susanne Davidson, Ankur Dixit, Fadzil Mohd Nor</t>
-  </si>
-  <si>
-    <t>Preprint / case study</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/339299525_Future_Hazard_Risks_Case_Study_Greenland_ice_sheet_mass_loss_Potential_consequences_for_mid-latitudes_with_a_focus_on_the_possibility_of_a_tsunami_occurrence_in_Scotland</t>
-  </si>
-  <si>
     <t>Presentation</t>
   </si>
   <si>
-    <t>Conference paper</t>
-  </si>
-  <si>
     <t>Global Warming Impacts on Glacier Dynamics in the Himalayan Basin</t>
   </si>
   <si>
-    <t>Ankur Dixit, Sandeep Sahany</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/339229061_Global_Warming_Impacts_on_Glacier_Dynamics_in_the_Himalayan_Basin</t>
-  </si>
-  <si>
-    <t>Time-frequency trade-off in image processing</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/332879123_Time-frequency_trade-off_in_image_processing</t>
-  </si>
-  <si>
     <t>Role of land-use-land-cover changes in the 2018 Mega-floods over Kerala (India)</t>
   </si>
   <si>
-    <t>Ankur Dixit, Sandeep Sahany, Sweta Choubey</t>
-  </si>
-  <si>
-    <t>Data / abstract</t>
-  </si>
-  <si>
-    <t>ACRS2015 Abstract DixitAnkur</t>
-  </si>
-  <si>
-    <t>Ankur Dixit, Praveen K. Thakur, Shiv P. Aggarwal</t>
-  </si>
-  <si>
-    <t>Conference abstract / data</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/303315634_ACRS2015_Abstract_DixitAnkur</t>
-  </si>
-  <si>
     <t>Ice sheet features identification, glacier velocity estimation, and glacier zones classification using high-resolution optical and SAR data</t>
   </si>
   <si>
-    <t>Praveen K. Thakur, Ankur Dixit, Arpit Chouksey, et al.</t>
-  </si>
-  <si>
-    <t>Proceedings of SPIE - The International Society for Optical Engineering</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/301912512_Ice_sheet_features_identification_glacier_velocity_estimation_and_glacier_zones_classification_using_high-resolution_optical_and_SAR_data</t>
-  </si>
-  <si>
     <t>Runoff Estimation for forthcoming years of Chambal River Basin, Using VIC and ARIMA Model</t>
   </si>
   <si>
-    <t>Ankur Dixit, Bhaskar R. Nikam, Vaibhav Garg, Shiv P. Aggarwal</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/303315377_Runoff_Estimation_for_forthcoming_years_of_Chambal_River_Basin_Using_VIC_and_ARIMA_Model</t>
-  </si>
-  <si>
     <t>Glacier velocity estimation and glacier zones classification using C and L-band SAR differential interferometry and classification techniques</t>
   </si>
   <si>
-    <t>Praveen K. Thakur, Ankur Dixit, Shiv P. Aggarwal</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/303381967_Glacier_velocity_estimation_and_glacier_zones_classification_using_C_and_L-band_SAR_differential_interferometry_and_classification_techniques</t>
-  </si>
-  <si>
     <t>High Resolution Digital Elevation creation using Tandem-x data in Snow and Glaciated Area</t>
   </si>
   <si>
-    <t>Praveen K. Thakur, Vaibhav Garg, Ankur Dixit, et al.</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/303381965_High_Resolution_Digital_Elevation_creation_using_Tandem-x_data_in_Snow_and_Glaciated_Area</t>
-  </si>
-  <si>
     <t>Snow, glacier and ice sheet studies using L and C-band SAR data in parts of Himalaya and Antarctic</t>
   </si>
   <si>
-    <t>Praveen K. Thakur, Arpit Chouksey, Ankur Dixit, Shiv P. Aggarwal</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/303381970_Snow_glacier_and_ice_sheet_studies_using_L_and_C-band_SAR_data_in_parts_of_Himalaya_and_Antarctic</t>
-  </si>
-  <si>
     <t>CLIMATE CHANGE IMPACT ON HYDROLOGY OF BEAS RIVER BASIN IN NORTH WESTERN HIMALAYA</t>
   </si>
   <si>
-    <t>ACRS 2015</t>
-  </si>
-  <si>
-    <t>Conference paper · Quezon City, Philippines</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/303315539_CLIMATE_CHANGE_IMPACT_ON_HYDROLOGY_OF_BEAS_RIVER_BASIN_IN_NORTH_WESTERN_HIMALAYA</t>
-  </si>
-  <si>
     <t>OPEN SOURCE GEOSPATIAL TOOLS FOR HYDROLOGICAL MODELING</t>
   </si>
   <si>
-    <t>Ankur Dixit, Praveen K. Thakur, Shiv P. Aggarwal, Sukant Jain</t>
-  </si>
-  <si>
-    <t>FOSS4G 2015</t>
-  </si>
-  <si>
-    <t>Conference paper · Dehradun, India</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/282572730_OPEN_SOURCE_GEOSPATIAL_TOOLS_FOR_HYDROLOGICAL_MODELING</t>
-  </si>
-  <si>
     <t>Thesis</t>
   </si>
   <si>
-    <t>Non-Linear Spectral Unmixing and Super-resolution Mapping of Hyperspectral Data</t>
-  </si>
-  <si>
-    <t>M.Tech thesis · DOI: 10.13140/RG.2.2.10660.50567</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/344672910_Non-Linear_Spectral_Unmixing_and_Super-resolution_Mapping_of_Hyperspectral_Data</t>
-  </si>
-  <si>
     <t>SPECTRAL UNMIXING AND SUPER-RESOLUTION MAPPING OF HYPERSPECTRAL DATA</t>
   </si>
   <si>
-    <t>M.Tech thesis presentation</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/347487563_SPECTRAL_UNMIXING_AND_SUPER-RESOLUTION_MAPPING_OF_HYPERSPECTRAL_DATA</t>
-  </si>
-  <si>
     <t>Comparison of various models and optimum range of its parameters used in SVM classification of digital satellite image</t>
-  </si>
-  <si>
-    <t>https://www.researchgate.net/publication/261458672_Comparison_of_various_models_and_optimum_range_of_its_parameters_used_in_SVM_classification_of_digital_satellite_image</t>
   </si>
   <si>
     <t>Mohanty, L. K., Sharma, P., Ahmed, R., &amp; Dixit, A.</t>
@@ -441,8 +279,119 @@
     <t>Mohanty, L. K., Gantayat, P., Dixit, A., Das Adhikari, M., Biswas, R., &amp; Singh, V. K.</t>
   </si>
   <si>
+    <t>https://doi.org/10.1038/s41598-026-35895-7</t>
+  </si>
+  <si>
+    <t>Mohanty, L. K., Tiwari, A., Kumar, A., Singh, V., &amp; Dixit, A.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s11069-025-07888-8</t>
+  </si>
+  <si>
+    <t>Dixit, A., Sahany, S., Mishra, S. K., &amp; Lehner, F.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1175/JHM-D-24-0096.1</t>
+  </si>
+  <si>
+    <t>Mohanty, L. K., Panda, B., Samantaray, S., Dixit, A., &amp; Bhange, S.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/s42452-024-05958-3</t>
+  </si>
+  <si>
+    <t>Dixit, A., Sahany, S., &amp; Mishra, S. K.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.jhydrol.2023.130219</t>
+  </si>
+  <si>
+    <t>Dixit, A., Sahany, S., Mishra, S. K., &amp; Mesquita, M. D. S.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1038/s41598-023-31353-w</t>
+  </si>
+  <si>
+    <t>Mohanty, L., Maiti, S., &amp; Dixit, A.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3389/feart.2022.1038777</t>
+  </si>
+  <si>
+    <t>Dixit, A., Sahany, S., Rajagopalan, B., &amp; Choubey, S.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.3354/cr01701</t>
+  </si>
+  <si>
+    <t>Sood, S., Thakur, P. K., Stein, A., Garg, V., &amp; Dixit, A.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.asr.2022.10.030</t>
+  </si>
+  <si>
+    <t>Dixit, A., Sahany, S., &amp; Kulkarni, A. V.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.jenvman.2021.113101</t>
+  </si>
+  <si>
+    <t>Dixit, A., &amp; Agarwal, S.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.acags.2021.100053</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1080/10106049.2020.1844312</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.rsase.2020.100374</t>
+  </si>
+  <si>
+    <t>Aggarwal, S. P., Thakur, P. K., Nikam, B. R., Garg, V., Chouksey, A., Dhote, P. R., Bisht, S., Dixit, A., Arora, S., Choudhury, A., Sharma, V., Chauhan, P., &amp; Kumar, A. S.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.5194/isprs-archives-XLIII-B3-2020-853-2020</t>
+  </si>
+  <si>
+    <t>Biased mean states distort mountain climate change through snow-albedo feedbacks</t>
+  </si>
+  <si>
+    <t>Reframing the rarity of extreme low-snow years in the Upper Colorado River Basin</t>
+  </si>
+  <si>
+    <t>Contrasting dynamic and thermodynamic pathways shaped the 2024 Indian heatwave</t>
+  </si>
+  <si>
+    <t>Rahimi, S., Norris, J., Huang, L., Bass, B., Thackeray, C. W., Hall, A., Rhoades, A. M., Risser, M. D., Pierce, D. W., Cayan, D. R., Kalansky, J., Feldman, D., Adhikari, P., Geerts, B., Rasmussen, K. L., Liu, W., Lehner, F., Dixit, A., &amp; Lebo, Z. J.</t>
+  </si>
+  <si>
+    <t>Carr, S., Dixit, A., Lehner, F., Vano, J. A., Addor, N., Petach, T. N., &amp; Musselman, K. N.</t>
+  </si>
+  <si>
+    <t>Role of Earth Observation Data and Hydrological Modeling in Supporting UN SDGs in North West Himalaya.</t>
+  </si>
+  <si>
+    <t>Submitted</t>
+  </si>
+  <si>
+    <t>Dixit, A., Najibi, N., Mishra, N., Dixit, A., &amp; Lehner, F.</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1007/978-981-92-0835-7_1</t>
+  </si>
+  <si>
+    <t>16th Annual Meeting of the Asia Oceania Geosciences Society (AOGS)</t>
+  </si>
+  <si>
+    <t>Singapore, 28 July–2 August 2019</t>
+  </si>
+  <si>
+    <t>EGU General Assembly 2019</t>
+  </si>
+  <si>
     <r>
-      <t>16</t>
+      <t>Proceedings of SPIE, Vol. 9877</t>
     </r>
     <r>
       <rPr>
@@ -450,45 +399,150 @@
         <color theme="1"/>
         <rFont val="Aptos Narrow"/>
       </rPr>
-      <t>, 9741.</t>
+      <t>, Article 987719, pp. 987719-1–987719-16.</t>
     </r>
   </si>
   <si>
-    <t>https://doi.org/10.1038/s41598-026-35895-7</t>
-  </si>
-  <si>
-    <t>Mohanty, L. K., Tiwari, A., Kumar, A., Singh, V., &amp; Dixit, A.</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s11069-025-07888-8</t>
-  </si>
-  <si>
-    <t>Dixit, A., Sahany, S., Mishra, S. K., &amp; Lehner, F.</t>
+    <t>SPIE Asia-Pacific Remote Sensing 2016, New Delhi, India</t>
+  </si>
+  <si>
+    <t>Thakur, P. K., Dixit, A., Chouksey, A., Aggarwal, S. P., &amp; Kumar, A. S.</t>
+  </si>
+  <si>
+    <t>Dixit, A., Nikam, B. R., Aggarwal, S. P., Garg, V., Gupta, P. K., &amp; Thakur, P. K.</t>
+  </si>
+  <si>
+    <t>HYDRO-2015 INTERNATIONAL</t>
+  </si>
+  <si>
+    <t>36th Asian Conference on Remote Sensing (ACRS 2015)</t>
+  </si>
+  <si>
+    <t>Thakur, P. K., Dixit, A., &amp; Aggarwal, S. P.</t>
+  </si>
+  <si>
+    <t>Thakur, P. K., Garg, V., Dixit, A., Chatterjee, R. S., Aggarwal, S. P., &amp; Snehmani.</t>
+  </si>
+  <si>
+    <t>11th International Conference on Microwaves, Antenna, Propagation &amp; Remote Sensing (ICMARS 2015)</t>
+  </si>
+  <si>
+    <t>Thakur, P. K., Chouksey, A., Dixit, A., &amp; Aggarwal, S. P.</t>
+  </si>
+  <si>
+    <t>NASA–ISRO Synthetic Aperture Radar (NISAR) Science Workshop</t>
+  </si>
+  <si>
+    <t>Dixit, A., Thakur, P. K., &amp; Aggarwal, S. P.</t>
+  </si>
+  <si>
+    <t>Dixit, A., Thakur, P. K., Aggarwal, S. P., &amp; Jain, S.</t>
+  </si>
+  <si>
+    <t>OSGEO-India: FOSS4G 2015</t>
+  </si>
+  <si>
+    <t>2013 IEEE Second International Conference on Image Information Processing (ICIIP-2013)</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1109/ICIIP.2013.6707616</t>
+  </si>
+  <si>
+    <t>AGU Frontiers in Hydrology: Future of Water Meeting</t>
+  </si>
+  <si>
+    <t>Davidson, S., Dixit, A., &amp; Mohd Nor, F.</t>
+  </si>
+  <si>
+    <t>APECS–APPLICATE–YOPP Online Course 2019</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.13140/RG.2.2.15196.54401</t>
+  </si>
+  <si>
+    <t>M.Tech. thesis</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.13140/RG.2.2.10660.50567</t>
+  </si>
+  <si>
+    <t>Dixit A.,  Sahany S.</t>
+  </si>
+  <si>
+    <t>Dixit A.,  Sahany S., Choubey S.</t>
+  </si>
+  <si>
+    <t>Report</t>
+  </si>
+  <si>
+    <t>16, 9741.</t>
+  </si>
+  <si>
+    <t>26(3), 345–363.</t>
+  </si>
+  <si>
+    <t>6, 363.</t>
+  </si>
+  <si>
+    <t>13, 4756.</t>
+  </si>
+  <si>
+    <t>10, 1038777.</t>
+  </si>
+  <si>
+    <t>89, 1–14.</t>
+  </si>
+  <si>
+    <t>70(12), 3975–3999.</t>
+  </si>
+  <si>
+    <t>9, 100053.</t>
+  </si>
+  <si>
+    <t>37(10), 3033–3050.</t>
+  </si>
+  <si>
+    <t>XLIII-B3-2020, 853–860.</t>
+  </si>
+  <si>
+    <t>20, 100374.</t>
+  </si>
+  <si>
+    <t>Vienna, Austria, 7–12 April 2019</t>
+  </si>
+  <si>
+    <t>IIT Roorkee, Roorkee, India, 17–19 December 2015.</t>
+  </si>
+  <si>
+    <t>Metro Manila, Philippines, 19–23 October 2015.</t>
+  </si>
+  <si>
+    <t>Jodhpur, Rajasthan, India, 15–17 December 2015.</t>
+  </si>
+  <si>
+    <t>Space Applications Centre (ISRO), Ahmedabad, India, 19–20 November 2015.</t>
+  </si>
+  <si>
+    <t>Quezon City, Metro Manila, Philippines, October 2015.</t>
+  </si>
+  <si>
+    <t>Dehradun, India, 8–10 June 2015.</t>
+  </si>
+  <si>
+    <t>Shimla, Himachal Pradesh, India, 9–11 December 2013. IEEE.</t>
+  </si>
+  <si>
+    <t>San Juan, Puerto Rico, 19–24 June 2022.</t>
+  </si>
+  <si>
+    <t>2019 case study,</t>
+  </si>
+  <si>
+    <t>Indian Institute of Remote Sensing, Dehradun, India, August 2014.</t>
   </si>
   <si>
     <r>
-      <t>26</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>(3), 345–363.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>122</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>(4)</t>
+      <t>122(4)</t>
     </r>
     <r>
       <rPr>
@@ -500,216 +554,12 @@
       <t>.</t>
     </r>
   </si>
-  <si>
-    <t>https://doi.org/10.1175/JHM-D-24-0096.1</t>
-  </si>
-  <si>
-    <t>Mohanty, L. K., Panda, B., Samantaray, S., Dixit, A., &amp; Bhange, S.</t>
-  </si>
-  <si>
-    <r>
-      <t>6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>, 363.</t>
-    </r>
-  </si>
-  <si>
-    <t>https://doi.org/10.1007/s42452-024-05958-3</t>
-  </si>
-  <si>
-    <t>Dixit, A., Sahany, S., &amp; Mishra, S. K.</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.jhydrol.2023.130219</t>
-  </si>
-  <si>
-    <t>Dixit, A., Sahany, S., Mishra, S. K., &amp; Mesquita, M. D. S.</t>
-  </si>
-  <si>
-    <r>
-      <t>13</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>, 4756.</t>
-    </r>
-  </si>
-  <si>
-    <t>https://doi.org/10.1038/s41598-023-31353-w</t>
-  </si>
-  <si>
-    <t>Mohanty, L., Maiti, S., &amp; Dixit, A.</t>
-  </si>
-  <si>
-    <r>
-      <t>10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>, 1038777.</t>
-    </r>
-  </si>
-  <si>
-    <t>https://doi.org/10.3389/feart.2022.1038777</t>
-  </si>
-  <si>
-    <t>Dixit, A., Sahany, S., Rajagopalan, B., &amp; Choubey, S.</t>
-  </si>
-  <si>
-    <r>
-      <t>89</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>, 1–14.</t>
-    </r>
-  </si>
-  <si>
-    <t>https://doi.org/10.3354/cr01701</t>
-  </si>
-  <si>
-    <t>Sood, S., Thakur, P. K., Stein, A., Garg, V., &amp; Dixit, A.</t>
-  </si>
-  <si>
-    <r>
-      <t>70</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>(12), 3975–3999.</t>
-    </r>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.asr.2022.10.030</t>
-  </si>
-  <si>
-    <t>Dixit, A., Sahany, S., &amp; Kulkarni, A. V.</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.jenvman.2021.113101</t>
-  </si>
-  <si>
-    <t>Dixit, A., &amp; Agarwal, S.</t>
-  </si>
-  <si>
-    <r>
-      <t>9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>, 100053.</t>
-    </r>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.acags.2021.100053</t>
-  </si>
-  <si>
-    <t>https://doi.org/10.1080/10106049.2020.1844312</t>
-  </si>
-  <si>
-    <r>
-      <t>37</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>(10), 3033–3050.</t>
-    </r>
-  </si>
-  <si>
-    <t>https://doi.org/10.1016/j.rsase.2020.100374</t>
-  </si>
-  <si>
-    <r>
-      <t>20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>, 100374.</t>
-    </r>
-  </si>
-  <si>
-    <t>Aggarwal, S. P., Thakur, P. K., Nikam, B. R., Garg, V., Chouksey, A., Dhote, P. R., Bisht, S., Dixit, A., Arora, S., Choudhury, A., Sharma, V., Chauhan, P., &amp; Kumar, A. S.</t>
-  </si>
-  <si>
-    <r>
-      <t>XLIII-B3-2020</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-      </rPr>
-      <t>, 853–860.</t>
-    </r>
-  </si>
-  <si>
-    <t>https://doi.org/10.5194/isprs-archives-XLIII-B3-2020-853-2020</t>
-  </si>
-  <si>
-    <t>Biased mean states distort mountain climate change through snow-albedo feedbacks</t>
-  </si>
-  <si>
-    <t>Reframing the rarity of extreme low-snow years in the Upper Colorado River Basin</t>
-  </si>
-  <si>
-    <t>Contrasting dynamic and thermodynamic pathways shaped the 2024 Indian heatwave</t>
-  </si>
-  <si>
-    <t>Rahimi, S., Norris, J., Huang, L., Bass, B., Thackeray, C. W., Hall, A., Rhoades, A. M., Risser, M. D., Pierce, D. W., Cayan, D. R., Kalansky, J., Feldman, D., Adhikari, P., Geerts, B., Rasmussen, K. L., Liu, W., Lehner, F., Dixit, A., &amp; Lebo, Z. J.</t>
-  </si>
-  <si>
-    <t>Carr, S., Dixit, A., Lehner, F., Vano, J. A., Addor, N., Petach, T. N., &amp; Musselman, K. N.</t>
-  </si>
-  <si>
-    <t>Role of Earth Observation Data and Hydrological Modeling in Supporting UN SDGs in North West Himalaya.</t>
-  </si>
-  <si>
-    <t>Submitted</t>
-  </si>
-  <si>
-    <t>Dixit, A., Najibi, N., Mishra, N., Dixit, A., &amp; Lehner, F.</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -740,6 +590,11 @@
       <color theme="1"/>
       <name val="Aptos Narrow"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -754,7 +609,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -778,34 +633,12 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -870,26 +703,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -898,7 +731,40 @@
   </cellStyles>
   <dxfs count="10">
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
+      <font>
+        <b val="0"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -909,12 +775,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -922,53 +782,7 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -1123,10 +937,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PublicationsTable" displayName="PublicationsTable" ref="A1:I48" totalsRowShown="0" headerRowDxfId="9">
-  <autoFilter ref="A1:I48" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I48">
-    <sortCondition ref="C1:C48"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PublicationsTable" displayName="PublicationsTable" ref="A1:I42" totalsRowShown="0" headerRowDxfId="9">
+  <autoFilter ref="A1:I42" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I42">
+    <sortCondition ref="C1:C42"/>
   </sortState>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Year" dataDxfId="8"/>
@@ -1134,10 +948,10 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Type_str" dataDxfId="6"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Title" dataDxfId="5"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Authors" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Venue" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Details" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Venue" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Details" dataDxfId="0"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="URL" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Display" dataDxfId="0"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Display" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1338,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="3" customWidth="1"/>
@@ -1387,137 +1201,137 @@
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="4"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="13"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="10"/>
+      <c r="I2" s="8"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="12"/>
+      <c r="A3" s="10"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
-      <c r="G3" s="4"/>
+      <c r="G3" s="13"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="13"/>
+      <c r="I3" s="11"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="12"/>
+      <c r="A4" s="10"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="G4" s="4"/>
+      <c r="G4" s="13"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="13"/>
+      <c r="I4" s="11"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="12"/>
+      <c r="A5" s="10"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
-      <c r="G5" s="4"/>
+      <c r="G5" s="13"/>
       <c r="H5" s="4"/>
-      <c r="I5" s="13"/>
+      <c r="I5" s="11"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="12"/>
+      <c r="A6" s="10"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
-      <c r="G6" s="4"/>
+      <c r="G6" s="13"/>
       <c r="H6" s="4"/>
-      <c r="I6" s="13"/>
+      <c r="I6" s="11"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="12"/>
+      <c r="A7" s="10"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
-      <c r="G7" s="4"/>
+      <c r="G7" s="13"/>
       <c r="H7" s="4"/>
-      <c r="I7" s="13"/>
+      <c r="I7" s="11"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="12"/>
+      <c r="A8" s="10"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
-      <c r="G8" s="4"/>
+      <c r="G8" s="13"/>
       <c r="H8" s="4"/>
-      <c r="I8" s="13"/>
+      <c r="I8" s="11"/>
     </row>
     <row r="9" spans="1:9" ht="34">
       <c r="A9" s="4" t="s">
-        <v>172</v>
+        <v>106</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>172</v>
+        <v>106</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>168</v>
+        <v>102</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="G9" s="4"/>
+        <v>107</v>
+      </c>
+      <c r="G9" s="13"/>
       <c r="H9" s="4"/>
-      <c r="I9" s="10" t="s">
-        <v>14</v>
+      <c r="I9" s="8" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="34">
       <c r="A10" s="4" t="s">
-        <v>172</v>
+        <v>106</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>172</v>
+        <v>106</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>167</v>
+        <v>101</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>170</v>
+        <v>104</v>
       </c>
       <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
+      <c r="G10" s="13"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="102">
       <c r="A11" s="4" t="s">
-        <v>172</v>
+        <v>106</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>172</v>
+        <v>106</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>166</v>
+        <v>100</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>169</v>
+        <v>103</v>
       </c>
       <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
+      <c r="G11" s="13"/>
       <c r="H11" s="4"/>
       <c r="I11" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="68">
@@ -1525,28 +1339,28 @@
         <v>2026</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="D12" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>122</v>
+        <v>69</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>68</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="34">
@@ -1554,28 +1368,28 @@
         <v>2026</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="D13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>126</v>
+      <c r="G13" s="13" t="s">
+        <v>72</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>127</v>
+        <v>73</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="34">
@@ -1583,28 +1397,28 @@
         <v>2026</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="D14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>129</v>
+      <c r="G14" s="13" t="s">
+        <v>137</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>130</v>
+        <v>75</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="34">
@@ -1612,28 +1426,28 @@
         <v>2026</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="D15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E15" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>135</v>
+      <c r="G15" s="13" t="s">
+        <v>159</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="34">
@@ -1641,28 +1455,28 @@
         <v>2025</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="D16" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>134</v>
+        <v>78</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>138</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="34">
@@ -1670,28 +1484,28 @@
         <v>2024</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="D17" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>138</v>
+        <v>80</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>139</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>139</v>
+        <v>81</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="51">
@@ -1699,28 +1513,28 @@
         <v>2023</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="D18" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E18" t="s">
-        <v>140</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>37</v>
+        <v>28</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>30</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>141</v>
+        <v>83</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="34">
@@ -1728,28 +1542,28 @@
         <v>2023</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="D19" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>143</v>
+        <v>84</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>140</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="34">
@@ -1757,28 +1571,28 @@
         <v>2023</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="D20" s="4" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>146</v>
+        <v>86</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>141</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="34">
@@ -1786,28 +1600,28 @@
         <v>2022</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="D21" s="4" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>149</v>
+        <v>88</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>142</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>150</v>
+        <v>89</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="51">
@@ -1815,28 +1629,28 @@
         <v>2022</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>152</v>
+        <v>90</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>143</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>153</v>
+        <v>91</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="34">
@@ -1844,28 +1658,28 @@
         <v>2021</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="D23" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>58</v>
+        <v>92</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>43</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>155</v>
+        <v>93</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="34">
@@ -1873,28 +1687,28 @@
         <v>2021</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="D24" s="2" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>157</v>
+        <v>94</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>144</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="34">
@@ -1902,28 +1716,28 @@
         <v>2020</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="D25" s="2" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>160</v>
+        <v>94</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>145</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>159</v>
+        <v>96</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="68">
@@ -1931,28 +1745,28 @@
         <v>2020</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="D26" s="2" t="s">
-        <v>171</v>
+        <v>105</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>164</v>
+        <v>98</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>146</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>165</v>
+        <v>99</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="34">
@@ -1960,608 +1774,471 @@
         <v>2020</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="D27" s="2" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>162</v>
+        <v>94</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>147</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>161</v>
+        <v>97</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="85">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="51">
       <c r="A28" s="4">
         <v>2026</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="F28" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="F28" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G28" s="4" t="s">
-        <v>120</v>
+      <c r="G28" s="13" t="s">
+        <v>66</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>13</v>
+        <v>108</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="51">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="34">
       <c r="A29" s="2">
         <v>2019</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>75</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="H29" s="4"/>
       <c r="I29" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="51">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="34">
       <c r="A30" s="2">
         <v>2019</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>77</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="H30" s="4"/>
       <c r="I30" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="85">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="51">
       <c r="A31" s="2">
         <v>2016</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>88</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="H31" s="4"/>
       <c r="I31" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="68">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="51">
       <c r="A32" s="2">
         <v>2015</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>72</v>
+        <v>52</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>91</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="G32" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="H32" s="4"/>
       <c r="I32" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="85">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="51">
       <c r="A33" s="2">
         <v>2015</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>72</v>
+        <v>52</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>94</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="H33" s="4"/>
       <c r="I33" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" ht="68">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="51">
       <c r="A34" s="2">
         <v>2015</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>72</v>
+        <v>52</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>97</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="H34" s="4"/>
       <c r="I34" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" ht="85">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="68">
       <c r="A35" s="2">
         <v>2015</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>72</v>
+        <v>52</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>100</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="H35" s="4"/>
       <c r="I35" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="68">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="51">
       <c r="A36" s="2">
         <v>2015</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>72</v>
+        <v>52</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>104</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="H36" s="4"/>
       <c r="I36" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="51">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="34">
       <c r="A37" s="2">
         <v>2015</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>72</v>
+        <v>52</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>109</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="H37" s="4"/>
       <c r="I37" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" ht="85">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="51">
       <c r="A38" s="2">
         <v>2013</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>72</v>
+        <v>52</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>118</v>
+        <v>64</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>127</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" ht="85">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="51">
       <c r="A39" s="2">
-        <v>2013</v>
+        <v>2022</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>72</v>
+        <v>38</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>118</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="H39" s="4"/>
       <c r="I39" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="34">
       <c r="A40" s="2">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>80</v>
+        <v>38</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>38</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E40" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E40" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>84</v>
-      </c>
+      <c r="F40" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="H40" s="4"/>
       <c r="I40" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" ht="85">
-      <c r="A41" s="4">
-        <v>2024</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="51">
+      <c r="A41" s="2">
+        <v>2019</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>28</v>
+      <c r="C41" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4" t="s">
-        <v>30</v>
+        <v>129</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G41" s="13" t="s">
+        <v>157</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" ht="85">
+        <v>131</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="51">
       <c r="A42" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>50</v>
+        <v>2014</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>53</v>
+        <v>63</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>133</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" ht="68">
-      <c r="A43" s="2">
-        <v>2022</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="102">
-      <c r="A44" s="2">
-        <v>2019</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="51">
-      <c r="A45" s="2">
-        <v>2019</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="85">
-      <c r="A46" s="2">
-        <v>2014</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="51">
-      <c r="A47" s="4">
-        <v>2022</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" ht="68">
-      <c r="A48" s="5">
-        <v>2014</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="I48" s="7" t="s">
-        <v>14</v>
-      </c>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="D43" s="2"/>
+      <c r="F43" s="7"/>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="F44" s="7"/>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="F45" s="7"/>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="F46" s="7"/>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="F47" s="7"/>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="F48" s="7"/>
+    </row>
+    <row r="49" spans="6:6">
+      <c r="F49" s="7"/>
+    </row>
+    <row r="50" spans="6:6">
+      <c r="F50" s="7"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="B12:B48 C2:C9" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="C2:C9 C29:C31 B12:B42" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Articles,Presentation,Poster,Reports/Chapter,Seminar/Invited talk"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ankurdixit/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D880BA5A-0B72-8D47-9915-68F92DAA0C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85E911F7-82A2-C84A-801E-D70F69FA77DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3340" yWindow="1200" windowWidth="38400" windowHeight="20120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Publications" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="210">
   <si>
     <t>Year</t>
   </si>
@@ -553,6 +553,156 @@
       </rPr>
       <t>.</t>
     </r>
+  </si>
+  <si>
+    <t>The potential for emergent constraints on hydroclimate projections over the Southwestern US</t>
+  </si>
+  <si>
+    <t>Lehner, F., Dixit, A., Kim, H., &amp; Kuo, Y. N.</t>
+  </si>
+  <si>
+    <t>AGU Fall Meeting Abstracts 2025, GC51H-0295</t>
+  </si>
+  <si>
+    <t>New Orleans, LA, USA, December 2025</t>
+  </si>
+  <si>
+    <t>Trends in Emerging Climate Change Signals in Upper Colorado River Basin Snow Water Resources</t>
+  </si>
+  <si>
+    <t>Carr, S., Dixit, A., Lehner, F., Addor, N., Vano, J. A., Petach, T., &amp; Musselman, K. N.</t>
+  </si>
+  <si>
+    <t>AGU Fall Meeting Abstracts 2025, C41A-05</t>
+  </si>
+  <si>
+    <t>Upper Colorado River Snowpack Potentially More Resilient than Climate Models Suggest</t>
+  </si>
+  <si>
+    <t>Dixit, A., Musselman, K. N., Addor, N., Carr, S., Gutmann, E. D., Huang, L., et al.</t>
+  </si>
+  <si>
+    <t>AGU Fall Meeting Abstracts 2025, GC43O-0985</t>
+  </si>
+  <si>
+    <t>Influence of Long-Term Trends in Tropical Pacific Sea Surface Temperature on Atmospheric River Statistics in Western North America</t>
+  </si>
+  <si>
+    <t>Kwong, A., Dixit, A., &amp; Lehner, F.</t>
+  </si>
+  <si>
+    <t>105th Annual AMS Meeting 2025, 456633</t>
+  </si>
+  <si>
+    <t>Impact of Tropical Pacific SST Variability on Atmospheric River Patterns in Western North America</t>
+  </si>
+  <si>
+    <t>105th Annual AMS Meeting 2025, 458788</t>
+  </si>
+  <si>
+    <t>Multihazard Early Warning System in the Himalayan Region: From Early Warning to Early Action</t>
+  </si>
+  <si>
+    <t>Srivastava, P., Sen, S., Subramanian, S. S., Shukla, R., &amp; Dixit, A.</t>
+  </si>
+  <si>
+    <t>AGU24</t>
+  </si>
+  <si>
+    <t>Washington, DC, USA, December 2024</t>
+  </si>
+  <si>
+    <t>Understanding the Causality of the 2024 Long-Lasting Heatwave Over India: The Role of Anthropogenic Climate Change and Natural Climate Variability</t>
+  </si>
+  <si>
+    <t>Dixit, A., Najibi, N., &amp; Lehner, F.</t>
+  </si>
+  <si>
+    <t>AGU Fall Meeting Abstracts 2024, A44H-06</t>
+  </si>
+  <si>
+    <t>Assessing the Accuracy of IMDAA over ERA5 Reanalysis Data in Capturing Extreme Dry, Wet, and Heat Wave Days Across Homogeneous Monsoon Regions of India</t>
+  </si>
+  <si>
+    <t>Barsinge, A., Singh, V. K., Dixit, A., &amp; Chandra, V.</t>
+  </si>
+  <si>
+    <t>AGU Fall Meeting Abstracts 2024, NH31F-217</t>
+  </si>
+  <si>
+    <t>Model resolution sensitivity of time of emergence for snow metrics in the Upper Colorado River Basin</t>
+  </si>
+  <si>
+    <t>Dixit, A., Rahimi, S., Huang, L., Addor, N., Vano, J. A., Musselman, K. N., &amp; Lehner, F.</t>
+  </si>
+  <si>
+    <t>AGU Fall Meeting Abstracts 2024, GC23J-03</t>
+  </si>
+  <si>
+    <t>Model resolution dependence of snow-water resilience to climate change in the Upper Colorado River Basin</t>
+  </si>
+  <si>
+    <t>Dixit, A., Rahimi, S., Huang, L., Collins, E., Addor, N., Vano, J. A., Musselman, K. N., et al.</t>
+  </si>
+  <si>
+    <t>AGU Fall Meeting Abstracts 2023, A23U-06</t>
+  </si>
+  <si>
+    <t>San Francisco, CA, USA, December 2023</t>
+  </si>
+  <si>
+    <t>Investigating Parameter Sensitivity in WRF-Hydro for Streamflow Modeling over the North-Western Himalayan Basin</t>
+  </si>
+  <si>
+    <t>Dixit, A., &amp; Sahany, S.</t>
+  </si>
+  <si>
+    <t>AGU Fall Meeting Abstracts 2018, H43D-2407</t>
+  </si>
+  <si>
+    <t>Washington, DC, USA, December 2018</t>
+  </si>
+  <si>
+    <t>New Orleans, Louisiana, USA, 12–16 January 2025</t>
+  </si>
+  <si>
+    <t>Report Chapter</t>
+  </si>
+  <si>
+    <t>Context of the Workshop</t>
+  </si>
+  <si>
+    <t>DOE (Department of Energy)</t>
+  </si>
+  <si>
+    <t>Understanding Decision-Relevant Regional Climate Data Products: Workshop Report, DOE/SC-2021</t>
+  </si>
+  <si>
+    <t>The State of Decision-Relevant Climate Data Production</t>
+  </si>
+  <si>
+    <t>The State of Knowledge on Users’ Climate Information Needs</t>
+  </si>
+  <si>
+    <t>The State of Benchmarking and Evaluation for Regional Climate Data Sets and Projections</t>
+  </si>
+  <si>
+    <t>Impact of Model Resolution on Snow Water Equivalent Trend Estimates Over the Upper Colorado River Basin</t>
+  </si>
+  <si>
+    <t>Dixit, A.</t>
+  </si>
+  <si>
+    <t>Cornell University–Atria University Symposium on Climate Change</t>
+  </si>
+  <si>
+    <t>Atria University, Bengaluru, India, 7 March 2025</t>
+  </si>
+  <si>
+    <t>Invited Talk</t>
+  </si>
+  <si>
+    <t>Seminar/Invited talk</t>
   </si>
 </sst>
 </file>
@@ -609,7 +759,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -684,11 +834,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -722,31 +894,36 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
     <dxf>
-      <font>
-        <b val="0"/>
-      </font>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
+        <right/>
         <top style="thin">
           <color indexed="64"/>
         </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -764,11 +941,16 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+      </font>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -778,7 +960,7 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -789,12 +971,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -937,8 +1113,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PublicationsTable" displayName="PublicationsTable" ref="A1:I42" totalsRowShown="0" headerRowDxfId="9">
-  <autoFilter ref="A1:I42" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="PublicationsTable" displayName="PublicationsTable" ref="A1:I58" totalsRowShown="0" headerRowDxfId="9">
+  <autoFilter ref="A1:I58" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I42">
     <sortCondition ref="C1:C42"/>
   </sortState>
@@ -948,10 +1124,10 @@
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Type_str" dataDxfId="6"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Title" dataDxfId="5"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Authors" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Venue" dataDxfId="2"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Details" dataDxfId="0"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Venue" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Details" dataDxfId="2"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="URL" dataDxfId="1"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Display" dataDxfId="3"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Display" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1152,7 +1328,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="3" customWidth="1"/>
@@ -1202,7 +1378,7 @@
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="9"/>
-      <c r="G2" s="13"/>
+      <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="8"/>
     </row>
@@ -1212,7 +1388,7 @@
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
-      <c r="G3" s="13"/>
+      <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="11"/>
     </row>
@@ -1222,7 +1398,7 @@
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="G4" s="13"/>
+      <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="11"/>
     </row>
@@ -1232,7 +1408,7 @@
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
-      <c r="G5" s="13"/>
+      <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="11"/>
     </row>
@@ -1242,7 +1418,7 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
-      <c r="G6" s="13"/>
+      <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="11"/>
     </row>
@@ -1252,7 +1428,7 @@
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
-      <c r="G7" s="13"/>
+      <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="11"/>
     </row>
@@ -1262,7 +1438,7 @@
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
-      <c r="G8" s="13"/>
+      <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="11"/>
     </row>
@@ -1282,7 +1458,7 @@
       <c r="E9" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="G9" s="13"/>
+      <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="8" t="s">
         <v>13</v>
@@ -1305,7 +1481,7 @@
         <v>104</v>
       </c>
       <c r="F10" s="4"/>
-      <c r="G10" s="13"/>
+      <c r="G10" s="4"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4" t="s">
         <v>13</v>
@@ -1328,7 +1504,7 @@
         <v>103</v>
       </c>
       <c r="F11" s="4"/>
-      <c r="G11" s="13"/>
+      <c r="G11" s="4"/>
       <c r="H11" s="4"/>
       <c r="I11" s="4" t="s">
         <v>13</v>
@@ -1353,7 +1529,7 @@
       <c r="F12" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="4" t="s">
         <v>68</v>
       </c>
       <c r="H12" s="4" t="s">
@@ -1382,7 +1558,7 @@
       <c r="F13" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="13" t="s">
+      <c r="G13" s="4" t="s">
         <v>72</v>
       </c>
       <c r="H13" s="4" t="s">
@@ -1411,7 +1587,7 @@
       <c r="F14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="13" t="s">
+      <c r="G14" s="4" t="s">
         <v>137</v>
       </c>
       <c r="H14" s="4" t="s">
@@ -1440,7 +1616,7 @@
       <c r="F15" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="4" t="s">
         <v>159</v>
       </c>
       <c r="H15" s="4" t="s">
@@ -1469,7 +1645,7 @@
       <c r="F16" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G16" s="13" t="s">
+      <c r="G16" s="4" t="s">
         <v>138</v>
       </c>
       <c r="H16" s="4" t="s">
@@ -1498,7 +1674,7 @@
       <c r="F17" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="G17" s="13" t="s">
+      <c r="G17" s="4" t="s">
         <v>139</v>
       </c>
       <c r="H17" s="4" t="s">
@@ -1527,7 +1703,7 @@
       <c r="F18" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G18" s="13" t="s">
+      <c r="G18" s="4" t="s">
         <v>30</v>
       </c>
       <c r="H18" s="4" t="s">
@@ -1556,7 +1732,7 @@
       <c r="F19" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G19" s="13" t="s">
+      <c r="G19" s="4" t="s">
         <v>140</v>
       </c>
       <c r="H19" s="4" t="s">
@@ -1585,7 +1761,7 @@
       <c r="F20" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G20" s="13" t="s">
+      <c r="G20" s="4" t="s">
         <v>141</v>
       </c>
       <c r="H20" s="4" t="s">
@@ -1614,7 +1790,7 @@
       <c r="F21" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G21" s="13" t="s">
+      <c r="G21" s="4" t="s">
         <v>142</v>
       </c>
       <c r="H21" s="4" t="s">
@@ -1643,7 +1819,7 @@
       <c r="F22" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="G22" s="13" t="s">
+      <c r="G22" s="4" t="s">
         <v>143</v>
       </c>
       <c r="H22" s="4" t="s">
@@ -1672,7 +1848,7 @@
       <c r="F23" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="G23" s="13" t="s">
+      <c r="G23" s="4" t="s">
         <v>43</v>
       </c>
       <c r="H23" s="4" t="s">
@@ -1701,7 +1877,7 @@
       <c r="F24" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G24" s="13" t="s">
+      <c r="G24" s="4" t="s">
         <v>144</v>
       </c>
       <c r="H24" s="4" t="s">
@@ -1730,7 +1906,7 @@
       <c r="F25" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="G25" s="13" t="s">
+      <c r="G25" s="4" t="s">
         <v>145</v>
       </c>
       <c r="H25" s="4" t="s">
@@ -1759,7 +1935,7 @@
       <c r="F26" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="G26" s="13" t="s">
+      <c r="G26" s="4" t="s">
         <v>146</v>
       </c>
       <c r="H26" s="4" t="s">
@@ -1788,7 +1964,7 @@
       <c r="F27" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="G27" s="13" t="s">
+      <c r="G27" s="4" t="s">
         <v>147</v>
       </c>
       <c r="H27" s="4" t="s">
@@ -1817,7 +1993,7 @@
       <c r="F28" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G28" s="13" t="s">
+      <c r="G28" s="4" t="s">
         <v>66</v>
       </c>
       <c r="H28" s="4" t="s">
@@ -1846,7 +2022,7 @@
       <c r="F29" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="G29" s="13" t="s">
+      <c r="G29" s="4" t="s">
         <v>110</v>
       </c>
       <c r="H29" s="4"/>
@@ -1873,7 +2049,7 @@
       <c r="F30" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="G30" s="4" t="s">
         <v>148</v>
       </c>
       <c r="H30" s="4"/>
@@ -1900,7 +2076,7 @@
       <c r="F31" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="G31" s="4" t="s">
         <v>113</v>
       </c>
       <c r="H31" s="4"/>
@@ -1927,7 +2103,7 @@
       <c r="F32" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="G32" s="4" t="s">
         <v>149</v>
       </c>
       <c r="H32" s="4"/>
@@ -1954,7 +2130,7 @@
       <c r="F33" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="G33" s="13" t="s">
+      <c r="G33" s="4" t="s">
         <v>150</v>
       </c>
       <c r="H33" s="4"/>
@@ -1981,7 +2157,7 @@
       <c r="F34" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="G34" s="13" t="s">
+      <c r="G34" s="4" t="s">
         <v>151</v>
       </c>
       <c r="H34" s="4"/>
@@ -2008,7 +2184,7 @@
       <c r="F35" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="G35" s="13" t="s">
+      <c r="G35" s="4" t="s">
         <v>152</v>
       </c>
       <c r="H35" s="4"/>
@@ -2035,7 +2211,7 @@
       <c r="F36" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="G36" s="13" t="s">
+      <c r="G36" s="4" t="s">
         <v>153</v>
       </c>
       <c r="H36" s="4"/>
@@ -2062,7 +2238,7 @@
       <c r="F37" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="G37" s="13" t="s">
+      <c r="G37" s="4" t="s">
         <v>154</v>
       </c>
       <c r="H37" s="4"/>
@@ -2089,7 +2265,7 @@
       <c r="F38" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="G38" s="13" t="s">
+      <c r="G38" s="4" t="s">
         <v>155</v>
       </c>
       <c r="H38" s="4" t="s">
@@ -2118,7 +2294,7 @@
       <c r="F39" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="G39" s="13" t="s">
+      <c r="G39" s="4" t="s">
         <v>156</v>
       </c>
       <c r="H39" s="4"/>
@@ -2145,7 +2321,7 @@
       <c r="F40" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="G40" s="13" t="s">
+      <c r="G40" s="4" t="s">
         <v>156</v>
       </c>
       <c r="H40" s="4"/>
@@ -2172,7 +2348,7 @@
       <c r="F41" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="G41" s="13" t="s">
+      <c r="G41" s="4" t="s">
         <v>157</v>
       </c>
       <c r="H41" s="4" t="s">
@@ -2201,7 +2377,7 @@
       <c r="F42" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="G42" s="13" t="s">
+      <c r="G42" s="4" t="s">
         <v>158</v>
       </c>
       <c r="H42" s="4" t="s">
@@ -2211,34 +2387,438 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
-      <c r="D43" s="2"/>
-      <c r="F43" s="7"/>
-    </row>
-    <row r="44" spans="1:9">
-      <c r="F44" s="7"/>
-    </row>
-    <row r="45" spans="1:9">
-      <c r="F45" s="7"/>
-    </row>
-    <row r="46" spans="1:9">
-      <c r="F46" s="7"/>
-    </row>
-    <row r="47" spans="1:9">
-      <c r="F47" s="7"/>
-    </row>
-    <row r="48" spans="1:9">
-      <c r="F48" s="7"/>
-    </row>
-    <row r="49" spans="6:6">
-      <c r="F49" s="7"/>
-    </row>
-    <row r="50" spans="6:6">
-      <c r="F50" s="7"/>
+    <row r="43" spans="1:9" ht="34">
+      <c r="A43" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="H43" s="13"/>
+      <c r="I43" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="34">
+      <c r="A44" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="H44" s="13"/>
+      <c r="I44" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="34">
+      <c r="A45" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="G45" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="H45" s="13"/>
+      <c r="I45" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="51">
+      <c r="A46" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="H46" s="13"/>
+      <c r="I46" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="34">
+      <c r="A47" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G47" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="H47" s="13"/>
+      <c r="I47" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="34">
+      <c r="A48" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H48" s="13"/>
+      <c r="I48" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="51">
+      <c r="A49" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H49" s="13"/>
+      <c r="I49" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="51">
+      <c r="A50" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="G50" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H50" s="13"/>
+      <c r="I50" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="34">
+      <c r="A51" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="H51" s="13"/>
+      <c r="I51" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="34">
+      <c r="A52" s="13">
+        <v>2023</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="H52" s="13"/>
+      <c r="I52" s="14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="34">
+      <c r="A53" s="16">
+        <v>2018</v>
+      </c>
+      <c r="B53" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="G53" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="H53" s="16"/>
+      <c r="I53" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="51">
+      <c r="A54" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="G54" s="15"/>
+      <c r="H54" s="13"/>
+      <c r="I54" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="51">
+      <c r="A55" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="G55" s="15"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="51">
+      <c r="A56" s="13">
+        <v>2024</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="G56" s="15"/>
+      <c r="H56" s="13"/>
+      <c r="I56" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="51">
+      <c r="A57" s="16">
+        <v>2024</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C57" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="G57" s="19"/>
+      <c r="H57" s="16"/>
+      <c r="I57" s="18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="51">
+      <c r="A58" s="16">
+        <v>2025</v>
+      </c>
+      <c r="B58" s="17" t="s">
+        <v>209</v>
+      </c>
+      <c r="C58" t="s">
+        <v>208</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E58" t="s">
+        <v>205</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="G58" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="H58" s="16"/>
+      <c r="I58" s="18"/>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="D59" s="2"/>
+      <c r="E59" s="4"/>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="E60" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="C2:C9 C29:C31 B12:B42" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="C2:C9 C29:C31 B12:B42 B54:B57" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Articles,Presentation,Poster,Reports/Chapter,Seminar/Invited talk"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/publications.xlsx
+++ b/data/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ankurdixit/website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85E911F7-82A2-C84A-801E-D70F69FA77DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A028A331-29F5-DA46-9128-05B3DBC8B48E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -375,9 +375,6 @@
     <t>Submitted</t>
   </si>
   <si>
-    <t>Dixit, A., Najibi, N., Mishra, N., Dixit, A., &amp; Lehner, F.</t>
-  </si>
-  <si>
     <t>https://doi.org/10.1007/978-981-92-0835-7_1</t>
   </si>
   <si>
@@ -703,6 +700,9 @@
   </si>
   <si>
     <t>Seminar/Invited talk</t>
+  </si>
+  <si>
+    <t>Dixit, A., Najibi, N., Mishra, N., Dixit, J., &amp; Lehner, F.</t>
   </si>
 </sst>
 </file>
@@ -860,7 +860,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -871,9 +871,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -896,11 +893,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1377,70 +1372,70 @@
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
-      <c r="F2" s="9"/>
+      <c r="F2" s="8"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-      <c r="I2" s="8"/>
+      <c r="I2" s="7"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="10"/>
+      <c r="A3" s="9"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
-      <c r="I3" s="11"/>
+      <c r="I3" s="10"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="10"/>
+      <c r="A4" s="9"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
-      <c r="I4" s="11"/>
+      <c r="I4" s="10"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="10"/>
+      <c r="A5" s="9"/>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
-      <c r="I5" s="11"/>
+      <c r="I5" s="10"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="10"/>
+      <c r="A6" s="9"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
-      <c r="I6" s="11"/>
+      <c r="I6" s="10"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="10"/>
+      <c r="A7" s="9"/>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
-      <c r="I7" s="11"/>
+      <c r="I7" s="10"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="10"/>
+      <c r="A8" s="9"/>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
-      <c r="I8" s="11"/>
+      <c r="I8" s="10"/>
     </row>
     <row r="9" spans="1:9" ht="34">
       <c r="A9" s="4" t="s">
@@ -1456,11 +1451,11 @@
         <v>102</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>107</v>
+        <v>209</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="7" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1526,7 +1521,7 @@
       <c r="E12" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="5" t="s">
         <v>67</v>
       </c>
       <c r="G12" s="4" t="s">
@@ -1555,7 +1550,7 @@
       <c r="E13" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="5" t="s">
         <v>19</v>
       </c>
       <c r="G13" s="4" t="s">
@@ -1584,11 +1579,11 @@
       <c r="E14" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="6" t="s">
         <v>17</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>75</v>
@@ -1613,11 +1608,11 @@
       <c r="E15" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F15" s="7" t="s">
+      <c r="F15" s="6" t="s">
         <v>21</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>77</v>
@@ -1642,11 +1637,11 @@
       <c r="E16" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F16" s="7" t="s">
+      <c r="F16" s="6" t="s">
         <v>24</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>79</v>
@@ -1671,11 +1666,11 @@
       <c r="E17" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F17" s="7" t="s">
+      <c r="F17" s="6" t="s">
         <v>27</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>81</v>
@@ -1700,7 +1695,7 @@
       <c r="E18" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="6" t="s">
         <v>29</v>
       </c>
       <c r="G18" s="4" t="s">
@@ -1729,11 +1724,11 @@
       <c r="E19" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="6" t="s">
         <v>17</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>85</v>
@@ -1758,11 +1753,11 @@
       <c r="E20" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="F20" s="7" t="s">
+      <c r="F20" s="6" t="s">
         <v>33</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>87</v>
@@ -1787,11 +1782,11 @@
       <c r="E21" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="F21" s="7" t="s">
+      <c r="F21" s="6" t="s">
         <v>35</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>89</v>
@@ -1816,11 +1811,11 @@
       <c r="E22" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="6" t="s">
         <v>37</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>91</v>
@@ -1845,7 +1840,7 @@
       <c r="E23" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F23" s="7" t="s">
+      <c r="F23" s="6" t="s">
         <v>42</v>
       </c>
       <c r="G23" s="4" t="s">
@@ -1874,11 +1869,11 @@
       <c r="E24" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F24" s="7" t="s">
+      <c r="F24" s="6" t="s">
         <v>45</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>95</v>
@@ -1903,11 +1898,11 @@
       <c r="E25" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F25" s="7" t="s">
+      <c r="F25" s="6" t="s">
         <v>47</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>96</v>
@@ -1932,11 +1927,11 @@
       <c r="E26" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="6" t="s">
         <v>48</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>99</v>
@@ -1961,11 +1956,11 @@
       <c r="E27" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" s="6" t="s">
         <v>50</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>97</v>
@@ -1990,14 +1985,14 @@
       <c r="E28" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" s="6" t="s">
         <v>12</v>
       </c>
       <c r="G28" s="4" t="s">
         <v>66</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I28" s="4" t="s">
         <v>13</v>
@@ -2017,13 +2012,13 @@
         <v>53</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="F29" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="H29" s="4"/>
       <c r="I29" s="2" t="s">
@@ -2044,13 +2039,13 @@
         <v>54</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>111</v>
+        <v>134</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H30" s="4"/>
       <c r="I30" s="2" t="s">
@@ -2071,13 +2066,13 @@
         <v>55</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="F31" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>113</v>
       </c>
       <c r="H31" s="4"/>
       <c r="I31" s="2" t="s">
@@ -2091,20 +2086,20 @@
       <c r="B32" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C32" s="12" t="s">
+      <c r="C32" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>56</v>
       </c>
       <c r="E32" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F32" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="F32" s="7" t="s">
-        <v>116</v>
-      </c>
       <c r="G32" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H32" s="4"/>
       <c r="I32" s="2" t="s">
@@ -2118,20 +2113,20 @@
       <c r="B33" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C33" s="12" t="s">
+      <c r="C33" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="F33" s="7" t="s">
         <v>117</v>
       </c>
+      <c r="F33" s="6" t="s">
+        <v>116</v>
+      </c>
       <c r="G33" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H33" s="4"/>
       <c r="I33" s="2" t="s">
@@ -2145,20 +2140,20 @@
       <c r="B34" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>58</v>
       </c>
       <c r="E34" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F34" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="F34" s="7" t="s">
-        <v>120</v>
-      </c>
       <c r="G34" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H34" s="4"/>
       <c r="I34" s="2" t="s">
@@ -2172,20 +2167,20 @@
       <c r="B35" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>59</v>
       </c>
       <c r="E35" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F35" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="F35" s="7" t="s">
-        <v>122</v>
-      </c>
       <c r="G35" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H35" s="4"/>
       <c r="I35" s="2" t="s">
@@ -2199,20 +2194,20 @@
       <c r="B36" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="12" t="s">
+      <c r="C36" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>60</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>117</v>
+        <v>122</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>116</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H36" s="4"/>
       <c r="I36" s="2" t="s">
@@ -2226,20 +2221,20 @@
       <c r="B37" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>61</v>
       </c>
       <c r="E37" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F37" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="F37" s="7" t="s">
-        <v>125</v>
-      </c>
       <c r="G37" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H37" s="4"/>
       <c r="I37" s="2" t="s">
@@ -2253,7 +2248,7 @@
       <c r="B38" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="11" t="s">
         <v>52</v>
       </c>
       <c r="D38" s="2" t="s">
@@ -2262,14 +2257,14 @@
       <c r="E38" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="H38" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>127</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>13</v>
@@ -2291,11 +2286,11 @@
       <c r="E39" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F39" s="7" t="s">
-        <v>128</v>
+      <c r="F39" s="6" t="s">
+        <v>127</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H39" s="4"/>
       <c r="I39" s="2" t="s">
@@ -2318,11 +2313,11 @@
       <c r="E40" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F40" s="7" t="s">
-        <v>128</v>
+      <c r="F40" s="6" t="s">
+        <v>127</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H40" s="4"/>
       <c r="I40" s="2" t="s">
@@ -2333,26 +2328,26 @@
       <c r="A41" s="2">
         <v>2019</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E41" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="F41" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="F41" s="7" t="s">
+      <c r="G41" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="H41" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>13</v>
@@ -2362,7 +2357,7 @@
       <c r="A42" s="2">
         <v>2014</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -2374,440 +2369,437 @@
       <c r="E42" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F42" s="7" t="s">
+      <c r="F42" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="G42" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="H42" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="G42" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="I42" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="34">
-      <c r="A43" s="13">
+      <c r="A43" s="12">
         <v>2025</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E43" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="F43" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="F43" s="7" t="s">
+      <c r="G43" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="H43" s="12"/>
+      <c r="I43" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="34">
+      <c r="A44" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="H43" s="13"/>
-      <c r="I43" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" ht="34">
-      <c r="A44" s="13">
+      <c r="E44" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="G44" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="H44" s="12"/>
+      <c r="I44" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="34">
+      <c r="A45" s="12">
         <v>2025</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="H44" s="13"/>
-      <c r="I44" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" ht="34">
-      <c r="A45" s="13">
-        <v>2025</v>
-      </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E45" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="F45" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="F45" s="7" t="s">
+      <c r="G45" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="H45" s="12"/>
+      <c r="I45" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="51">
+      <c r="A46" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="G45" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="H45" s="13"/>
-      <c r="I45" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" ht="51">
-      <c r="A46" s="13">
+      <c r="E46" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="H46" s="12"/>
+      <c r="I46" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="34">
+      <c r="A47" s="12">
         <v>2025</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D46" s="2" t="s">
+      <c r="B47" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E47" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="E46" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="H46" s="13"/>
-      <c r="I46" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" ht="34">
-      <c r="A47" s="13">
-        <v>2025</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D47" s="2" t="s">
+      <c r="F47" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="E47" s="4" t="s">
-        <v>171</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>174</v>
-      </c>
       <c r="G47" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="H47" s="13"/>
-      <c r="I47" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="H47" s="12"/>
+      <c r="I47" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="34">
-      <c r="A48" s="13">
+      <c r="A48" s="12">
         <v>2024</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E48" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="F48" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="F48" s="7" t="s">
+      <c r="G48" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="H48" s="12"/>
+      <c r="I48" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="51">
+      <c r="A49" s="12">
+        <v>2024</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="H48" s="13"/>
-      <c r="I48" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" ht="51">
-      <c r="A49" s="13">
+      <c r="E49" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="G49" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="H49" s="12"/>
+      <c r="I49" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="51">
+      <c r="A50" s="12">
         <v>2024</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="H49" s="13"/>
-      <c r="I49" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" ht="51">
-      <c r="A50" s="13">
-        <v>2024</v>
-      </c>
-      <c r="B50" s="3" t="s">
+      <c r="B50" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D50" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E50" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="F50" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="F50" s="7" t="s">
+      <c r="G50" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="H50" s="12"/>
+      <c r="I50" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="34">
+      <c r="A51" s="12">
+        <v>2024</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="G50" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="H50" s="13"/>
-      <c r="I50" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" ht="34">
-      <c r="A51" s="13">
-        <v>2024</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D51" s="2" t="s">
+      <c r="E51" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="F51" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="F51" s="7" t="s">
-        <v>187</v>
-      </c>
       <c r="G51" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="H51" s="13"/>
-      <c r="I51" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="H51" s="12"/>
+      <c r="I51" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="34">
-      <c r="A52" s="13">
+      <c r="A52" s="12">
         <v>2023</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B52" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>38</v>
       </c>
       <c r="D52" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E52" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="F52" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="F52" s="7" t="s">
+      <c r="G52" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="H52" s="12"/>
+      <c r="I52" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="34">
+      <c r="A53" s="14">
+        <v>2018</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="H52" s="13"/>
-      <c r="I52" s="14" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" ht="34">
-      <c r="A53" s="16">
-        <v>2018</v>
-      </c>
-      <c r="B53" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="C53" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="D53" s="2" t="s">
+      <c r="E53" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="F53" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="F53" s="7" t="s">
+      <c r="G53" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="G53" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="H53" s="16"/>
-      <c r="I53" s="18" t="s">
+      <c r="H53" s="14"/>
+      <c r="I53" s="16" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="51">
-      <c r="A54" s="13">
+      <c r="A54" s="12">
         <v>2024</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C54" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="E54" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="F54" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="F54" s="7" t="s">
+      <c r="H54" s="12"/>
+      <c r="I54" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="51">
+      <c r="A55" s="12">
+        <v>2024</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D55" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="G54" s="15"/>
-      <c r="H54" s="13"/>
-      <c r="I54" s="18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" ht="51">
-      <c r="A55" s="13">
+      <c r="E55" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H55" s="12"/>
+      <c r="I55" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="51">
+      <c r="A56" s="12">
         <v>2024</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B56" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C55" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D55" s="2" t="s">
+      <c r="C56" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="E55" s="4" t="s">
+      <c r="E56" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F56" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="F55" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="G55" s="15"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" ht="51">
-      <c r="A56" s="13">
+      <c r="H56" s="12"/>
+      <c r="I56" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="51">
+      <c r="A57" s="14">
         <v>2024</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B57" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C56" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="D56" s="2" t="s">
+      <c r="C57" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="E57" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="F57" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="F56" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="G56" s="15"/>
-      <c r="H56" s="13"/>
-      <c r="I56" s="18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" ht="51">
-      <c r="A57" s="16">
-        <v>2024</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C57" s="17" t="s">
-        <v>197</v>
-      </c>
-      <c r="D57" s="2" t="s">
+      <c r="G57" s="15"/>
+      <c r="H57" s="14"/>
+      <c r="I57" s="16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="51">
+      <c r="A58" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C58" t="s">
+        <v>207</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="E57" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="G57" s="19"/>
-      <c r="H57" s="16"/>
-      <c r="I57" s="18" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" ht="51">
-      <c r="A58" s="16">
-        <v>2025</v>
-      </c>
-      <c r="B58" s="17" t="s">
-        <v>209</v>
-      </c>
-      <c r="C58" t="s">
-        <v>208</v>
-      </c>
-      <c r="D58" s="2" t="s">
+      <c r="E58" t="s">
         <v>204</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="F58" s="7" t="s">
+      <c r="G58" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="G58" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="H58" s="16"/>
-      <c r="I58" s="18"/>
+      <c r="H58" s="14"/>
+      <c r="I58" s="16"/>
     </row>
     <row r="59" spans="1:9">
       <c r="D59" s="2"/>
